--- a/data/matriculas_santa_sofia_OFICIAL.xlsx
+++ b/data/matriculas_santa_sofia_OFICIAL.xlsx
@@ -28,7 +28,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -45,6 +45,11 @@
         <fgColor rgb="00F4CCCC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -58,10 +63,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -431,7 +437,6 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
           <t>BASE DE DATOS DE APARTAMENTOS Y REGISTRO DE MATRÍCULAS</t>
@@ -439,7 +444,6 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
           <t>Nota: Los coeficientes están actualizados según la Adición por Etapas de la Ley 675.</t>
@@ -447,7 +451,6 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
           <t>Bloque</t>
@@ -490,7 +493,6 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -533,7 +535,6 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -576,7 +577,6 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -619,7 +619,6 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -662,7 +661,6 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -705,7 +703,6 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -748,7 +745,6 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -791,7 +787,6 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -834,7 +829,6 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -877,7 +871,6 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -920,7 +913,6 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -963,7 +955,6 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -1006,7 +997,6 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -1049,7 +1039,6 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -1092,7 +1081,6 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -1135,7 +1123,6 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -1178,7 +1165,6 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -1221,7 +1207,6 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -1264,7 +1249,6 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -1307,7 +1291,6 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -1350,7 +1333,6 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -1393,7 +1375,6 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -1436,7 +1417,6 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -1479,7 +1459,6 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -1522,7 +1501,6 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -1565,7 +1543,6 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -1608,7 +1585,6 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -1651,7 +1627,6 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -1694,7 +1669,6 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -1737,7 +1711,6 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -1780,7 +1753,6 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -1823,7 +1795,6 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -1866,7 +1837,6 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -1909,7 +1879,6 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -1952,7 +1921,6 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -1995,7 +1963,6 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -2038,7 +2005,6 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -2081,7 +2047,6 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -2124,7 +2089,6 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -2167,7 +2131,6 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -2210,7 +2173,6 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -2253,7 +2215,6 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -2296,7 +2257,6 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -2339,7 +2299,6 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -2382,7 +2341,6 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -2425,7 +2383,6 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -2468,7 +2425,6 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -2511,7 +2467,6 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -2554,7 +2509,6 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -2597,7 +2551,6 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -2640,7 +2593,6 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -2683,7 +2635,6 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -2726,7 +2677,6 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -2769,7 +2719,6 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr"/>
       <c r="B59" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -2812,7 +2761,6 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -2855,7 +2803,6 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr"/>
       <c r="B61" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -2898,7 +2845,6 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -2941,7 +2887,6 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr"/>
       <c r="B63" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -2984,7 +2929,6 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -3027,7 +2971,6 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr"/>
       <c r="B65" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -3070,7 +3013,6 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -3113,7 +3055,6 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr"/>
       <c r="B67" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -3156,7 +3097,6 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr"/>
       <c r="B68" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -3199,7 +3139,6 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr"/>
       <c r="B69" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -3242,7 +3181,6 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -3285,7 +3223,6 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr"/>
       <c r="B71" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -3328,7 +3265,6 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -3371,7 +3307,6 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr"/>
       <c r="B73" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -3414,7 +3349,6 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr"/>
       <c r="B74" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -3457,7 +3391,6 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr"/>
       <c r="B75" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -3500,7 +3433,6 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr"/>
       <c r="B76" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -3543,7 +3475,6 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr"/>
       <c r="B77" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -3586,7 +3517,6 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr"/>
       <c r="B78" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -3629,7 +3559,6 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr"/>
       <c r="B79" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -3672,7 +3601,6 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr"/>
       <c r="B80" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -3715,7 +3643,6 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr"/>
       <c r="B81" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -3758,7 +3685,6 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr"/>
       <c r="B82" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -3801,7 +3727,6 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr"/>
       <c r="B83" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -3844,7 +3769,6 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr"/>
       <c r="B84" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -3887,7 +3811,6 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr"/>
       <c r="B85" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -3930,7 +3853,6 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr"/>
       <c r="B86" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -3973,7 +3895,6 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr"/>
       <c r="B87" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -4016,7 +3937,6 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr"/>
       <c r="B88" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -4059,7 +3979,6 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr"/>
       <c r="B89" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -4102,7 +4021,6 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr"/>
       <c r="B90" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -4145,7 +4063,6 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr"/>
       <c r="B91" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -4188,7 +4105,6 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr"/>
       <c r="B92" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -4231,7 +4147,6 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr"/>
       <c r="B93" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -4274,7 +4189,6 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr"/>
       <c r="B94" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -4317,7 +4231,6 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr"/>
       <c r="B95" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -4360,7 +4273,6 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr"/>
       <c r="B96" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -4403,7 +4315,6 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr"/>
       <c r="B97" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -4446,7 +4357,6 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr"/>
       <c r="B98" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -4489,7 +4399,6 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr"/>
       <c r="B99" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -4532,7 +4441,6 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr"/>
       <c r="B100" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -4575,7 +4483,6 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr"/>
       <c r="B101" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -4618,7 +4525,6 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr"/>
       <c r="B102" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -4661,7 +4567,6 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr"/>
       <c r="B103" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -4704,7 +4609,6 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr"/>
       <c r="B104" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -4747,7 +4651,6 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr"/>
       <c r="B105" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -4790,7 +4693,6 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr"/>
       <c r="B106" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -4833,7 +4735,6 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" t="inlineStr"/>
       <c r="B107" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -4876,7 +4777,6 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" t="inlineStr"/>
       <c r="B108" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -4919,7 +4819,6 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" t="inlineStr"/>
       <c r="B109" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -4962,7 +4861,6 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" t="inlineStr"/>
       <c r="B110" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -5005,7 +4903,6 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" t="inlineStr"/>
       <c r="B111" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -5048,7 +4945,6 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" t="inlineStr"/>
       <c r="B112" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -5091,7 +4987,6 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" t="inlineStr"/>
       <c r="B113" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -5134,7 +5029,6 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" t="inlineStr"/>
       <c r="B114" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -5177,7 +5071,6 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr"/>
       <c r="B115" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -5220,7 +5113,6 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" t="inlineStr"/>
       <c r="B116" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -5263,7 +5155,6 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" t="inlineStr"/>
       <c r="B117" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -5306,7 +5197,6 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" t="inlineStr"/>
       <c r="B118" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -5349,7 +5239,6 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" t="inlineStr"/>
       <c r="B119" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -5392,7 +5281,6 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" t="inlineStr"/>
       <c r="B120" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -5435,7 +5323,6 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" t="inlineStr"/>
       <c r="B121" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -5478,7 +5365,6 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="inlineStr"/>
       <c r="B122" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -5521,7 +5407,6 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" t="inlineStr"/>
       <c r="B123" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -5564,7 +5449,6 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" t="inlineStr"/>
       <c r="B124" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -5607,7 +5491,6 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" t="inlineStr"/>
       <c r="B125" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -5650,7 +5533,6 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" t="inlineStr"/>
       <c r="B126" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -5693,7 +5575,6 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" t="inlineStr"/>
       <c r="B127" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -5736,7 +5617,6 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" t="inlineStr"/>
       <c r="B128" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -5779,7 +5659,6 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" t="inlineStr"/>
       <c r="B129" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -5822,7 +5701,6 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" t="inlineStr"/>
       <c r="B130" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -5865,7 +5743,6 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" t="inlineStr"/>
       <c r="B131" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -5908,7 +5785,6 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" t="inlineStr"/>
       <c r="B132" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -5951,7 +5827,6 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" t="inlineStr"/>
       <c r="B133" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -5994,7 +5869,6 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" t="inlineStr"/>
       <c r="B134" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -6037,7 +5911,6 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" t="inlineStr"/>
       <c r="B135" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -6080,7 +5953,6 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" t="inlineStr"/>
       <c r="B136" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -6123,7 +5995,6 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" t="inlineStr"/>
       <c r="B137" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -6166,7 +6037,6 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" t="inlineStr"/>
       <c r="B138" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -6209,7 +6079,6 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" t="inlineStr"/>
       <c r="B139" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -6252,7 +6121,6 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" t="inlineStr"/>
       <c r="B140" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -6295,7 +6163,6 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" t="inlineStr"/>
       <c r="B141" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -6338,7 +6205,6 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" t="inlineStr"/>
       <c r="B142" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -6381,7 +6247,6 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" t="inlineStr"/>
       <c r="B143" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -6424,7 +6289,6 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" t="inlineStr"/>
       <c r="B144" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -6467,7 +6331,6 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" t="inlineStr"/>
       <c r="B145" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -6510,7 +6373,6 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" t="inlineStr"/>
       <c r="B146" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -6553,7 +6415,6 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" t="inlineStr"/>
       <c r="B147" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -6596,7 +6457,6 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" t="inlineStr"/>
       <c r="B148" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -6639,7 +6499,6 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" t="inlineStr"/>
       <c r="B149" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -6682,7 +6541,6 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" t="inlineStr"/>
       <c r="B150" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -6725,7 +6583,6 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" t="inlineStr"/>
       <c r="B151" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -6768,7 +6625,6 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" t="inlineStr"/>
       <c r="B152" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -6811,7 +6667,6 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" t="inlineStr"/>
       <c r="B153" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -6854,7 +6709,6 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" t="inlineStr"/>
       <c r="B154" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -6897,7 +6751,6 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" t="inlineStr"/>
       <c r="B155" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -6940,7 +6793,6 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" t="inlineStr"/>
       <c r="B156" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -6983,7 +6835,6 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" t="inlineStr"/>
       <c r="B157" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -7026,7 +6877,6 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" t="inlineStr"/>
       <c r="B158" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -7069,7 +6919,6 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" t="inlineStr"/>
       <c r="B159" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -7112,7 +6961,6 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" t="inlineStr"/>
       <c r="B160" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -7155,7 +7003,6 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" t="inlineStr"/>
       <c r="B161" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -7198,7 +7045,6 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" t="inlineStr"/>
       <c r="B162" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -7241,7 +7087,6 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" t="inlineStr"/>
       <c r="B163" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -7284,7 +7129,6 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" t="inlineStr"/>
       <c r="B164" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -7327,7 +7171,6 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" t="inlineStr"/>
       <c r="B165" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -7370,7 +7213,6 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" t="inlineStr"/>
       <c r="B166" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -7413,7 +7255,6 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" t="inlineStr"/>
       <c r="B167" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -7456,7 +7297,6 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" t="inlineStr"/>
       <c r="B168" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -7499,7 +7339,6 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" t="inlineStr"/>
       <c r="B169" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -7542,7 +7381,6 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" t="inlineStr"/>
       <c r="B170" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -7585,7 +7423,6 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" t="inlineStr"/>
       <c r="B171" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -7628,7 +7465,6 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" t="inlineStr"/>
       <c r="B172" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -7671,7 +7507,6 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" t="inlineStr"/>
       <c r="B173" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -7714,7 +7549,6 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" t="inlineStr"/>
       <c r="B174" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -7757,7 +7591,6 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" t="inlineStr"/>
       <c r="B175" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -7800,7 +7633,6 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" t="inlineStr"/>
       <c r="B176" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -7843,7 +7675,6 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" t="inlineStr"/>
       <c r="B177" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -7886,7 +7717,6 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" t="inlineStr"/>
       <c r="B178" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -7929,7 +7759,6 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" t="inlineStr"/>
       <c r="B179" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -7972,7 +7801,6 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" t="inlineStr"/>
       <c r="B180" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -8015,7 +7843,6 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" t="inlineStr"/>
       <c r="B181" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -8058,7 +7885,6 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" t="inlineStr"/>
       <c r="B182" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -8101,7 +7927,6 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" t="inlineStr"/>
       <c r="B183" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -8144,7 +7969,6 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" t="inlineStr"/>
       <c r="B184" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -8187,7 +8011,6 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" t="inlineStr"/>
       <c r="B185" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -8230,7 +8053,6 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" t="inlineStr"/>
       <c r="B186" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -8273,7 +8095,6 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" t="inlineStr"/>
       <c r="B187" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -8316,7 +8137,6 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" t="inlineStr"/>
       <c r="B188" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -8359,7 +8179,6 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" t="inlineStr"/>
       <c r="B189" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -8402,7 +8221,6 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" t="inlineStr"/>
       <c r="B190" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -8445,7 +8263,6 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" t="inlineStr"/>
       <c r="B191" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -8488,7 +8305,6 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" t="inlineStr"/>
       <c r="B192" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -8531,7 +8347,6 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" t="inlineStr"/>
       <c r="B193" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -8574,7 +8389,6 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" t="inlineStr"/>
       <c r="B194" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -8617,7 +8431,6 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" t="inlineStr"/>
       <c r="B195" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -8660,7 +8473,6 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" t="inlineStr"/>
       <c r="B196" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -8703,7 +8515,6 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" t="inlineStr"/>
       <c r="B197" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -8746,7 +8557,6 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" t="inlineStr"/>
       <c r="B198" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -8789,7 +8599,6 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" t="inlineStr"/>
       <c r="B199" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -8832,7 +8641,6 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" t="inlineStr"/>
       <c r="B200" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -8875,7 +8683,6 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" t="inlineStr"/>
       <c r="B201" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -8918,7 +8725,6 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" t="inlineStr"/>
       <c r="B202" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -8961,7 +8767,6 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" t="inlineStr"/>
       <c r="B203" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -9004,7 +8809,6 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" t="inlineStr"/>
       <c r="B204" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -9047,7 +8851,6 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" t="inlineStr"/>
       <c r="B205" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -9090,7 +8893,6 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" t="inlineStr"/>
       <c r="B206" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -9133,7 +8935,6 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" t="inlineStr"/>
       <c r="B207" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -9176,7 +8977,6 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" t="inlineStr"/>
       <c r="B208" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -9219,7 +9019,6 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" t="inlineStr"/>
       <c r="B209" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -9262,7 +9061,6 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" t="inlineStr"/>
       <c r="B210" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -9305,7 +9103,6 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" t="inlineStr"/>
       <c r="B211" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -9348,7 +9145,6 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" t="inlineStr"/>
       <c r="B212" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -9391,7 +9187,6 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" t="inlineStr"/>
       <c r="B213" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -9434,7 +9229,6 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" t="inlineStr"/>
       <c r="B214" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -9477,7 +9271,6 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" t="inlineStr"/>
       <c r="B215" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -9520,7 +9313,6 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" t="inlineStr"/>
       <c r="B216" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -9563,7 +9355,6 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" t="inlineStr"/>
       <c r="B217" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -9606,7 +9397,6 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" t="inlineStr"/>
       <c r="B218" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -9649,7 +9439,6 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" t="inlineStr"/>
       <c r="B219" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -9692,7 +9481,6 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" t="inlineStr"/>
       <c r="B220" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -9735,7 +9523,6 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" t="inlineStr"/>
       <c r="B221" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -9778,7 +9565,6 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" t="inlineStr"/>
       <c r="B222" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -9821,7 +9607,6 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" t="inlineStr"/>
       <c r="B223" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -9864,7 +9649,6 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" t="inlineStr"/>
       <c r="B224" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -9907,7 +9691,6 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" t="inlineStr"/>
       <c r="B225" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -9950,7 +9733,6 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" t="inlineStr"/>
       <c r="B226" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -9993,7 +9775,6 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" t="inlineStr"/>
       <c r="B227" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -10036,7 +9817,6 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" t="inlineStr"/>
       <c r="B228" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -10079,7 +9859,6 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" t="inlineStr"/>
       <c r="B229" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -10122,7 +9901,6 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" t="inlineStr"/>
       <c r="B230" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -10165,7 +9943,6 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" t="inlineStr"/>
       <c r="B231" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -10208,7 +9985,6 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" t="inlineStr"/>
       <c r="B232" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -10251,7 +10027,6 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" t="inlineStr"/>
       <c r="B233" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -10294,14 +10069,11 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" t="inlineStr"/>
       <c r="B234" t="inlineStr">
         <is>
           <t>TOTAL APARTAMENTOS (228)</t>
         </is>
       </c>
-      <c r="C234" t="inlineStr"/>
-      <c r="D234" t="inlineStr"/>
       <c r="E234" t="inlineStr">
         <is>
           <t>11,631.40</t>
@@ -10339,7 +10111,6 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
           <t>BASE DE DATOS DE PARQUEADEROS Y REGISTRO DE MATRÍCULAS</t>
@@ -10347,7 +10118,6 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
           <t>Nota: Incluye parqueaderos de carros (Sótano 1 y 2) y de motos (Fases 1 y 2).</t>
@@ -10355,7 +10125,6 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
           <t>Tipo</t>
@@ -10398,7 +10167,6 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -10441,7 +10209,6 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -10484,7 +10251,6 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -10527,7 +10293,6 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -10570,7 +10335,6 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -10613,7 +10377,6 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -10656,7 +10419,6 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -10699,7 +10461,6 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -10742,7 +10503,6 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -10785,7 +10545,6 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -10828,7 +10587,6 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -10871,7 +10629,6 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -10914,7 +10671,6 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -10957,7 +10713,6 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -11000,7 +10755,6 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -11043,7 +10797,6 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -11086,7 +10839,6 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -11129,7 +10881,6 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -11172,7 +10923,6 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -11215,7 +10965,6 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -11258,7 +11007,6 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -11301,7 +11049,6 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -11344,7 +11091,6 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -11387,7 +11133,6 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -11430,7 +11175,6 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -11473,7 +11217,6 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -11516,7 +11259,6 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -11559,7 +11301,6 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -11602,7 +11343,6 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -11645,7 +11385,6 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -11688,7 +11427,6 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -11731,7 +11469,6 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -11774,7 +11511,6 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -11817,7 +11553,6 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -11860,7 +11595,6 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -11903,7 +11637,6 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -11946,7 +11679,6 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -11989,7 +11721,6 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -12032,7 +11763,6 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -12075,7 +11805,6 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -12118,7 +11847,6 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -12161,7 +11889,6 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -12204,7 +11931,6 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -12247,7 +11973,6 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -12290,7 +12015,6 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -12333,7 +12057,6 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -12376,7 +12099,6 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -12419,7 +12141,6 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -12462,7 +12183,6 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -12505,7 +12225,6 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -12548,7 +12267,6 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -12591,7 +12309,6 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -12634,7 +12351,6 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -12677,7 +12393,6 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr"/>
       <c r="B59" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -12720,7 +12435,6 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -12763,7 +12477,6 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr"/>
       <c r="B61" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -12806,7 +12519,6 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -12849,7 +12561,6 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr"/>
       <c r="B63" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -12892,7 +12603,6 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -12935,7 +12645,6 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr"/>
       <c r="B65" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -12978,7 +12687,6 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -13021,7 +12729,6 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr"/>
       <c r="B67" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -13064,7 +12771,6 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr"/>
       <c r="B68" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -13107,7 +12813,6 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr"/>
       <c r="B69" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -13150,7 +12855,6 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -13193,7 +12897,6 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr"/>
       <c r="B71" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -13236,7 +12939,6 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -13279,7 +12981,6 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr"/>
       <c r="B73" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -13322,7 +13023,6 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr"/>
       <c r="B74" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -13365,7 +13065,6 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr"/>
       <c r="B75" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -13408,7 +13107,6 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr"/>
       <c r="B76" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -13451,7 +13149,6 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr"/>
       <c r="B77" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -13494,7 +13191,6 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr"/>
       <c r="B78" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -13537,7 +13233,6 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr"/>
       <c r="B79" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -13580,7 +13275,6 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr"/>
       <c r="B80" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -13623,7 +13317,6 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr"/>
       <c r="B81" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -13666,7 +13359,6 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr"/>
       <c r="B82" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -13709,7 +13401,6 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr"/>
       <c r="B83" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -13752,7 +13443,6 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr"/>
       <c r="B84" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -13795,7 +13485,6 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr"/>
       <c r="B85" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -13838,7 +13527,6 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr"/>
       <c r="B86" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -13881,7 +13569,6 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr"/>
       <c r="B87" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -13924,7 +13611,6 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr"/>
       <c r="B88" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -13967,7 +13653,6 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr"/>
       <c r="B89" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -14010,7 +13695,6 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr"/>
       <c r="B90" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -14053,7 +13737,6 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr"/>
       <c r="B91" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -14096,7 +13779,6 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr"/>
       <c r="B92" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -14139,7 +13821,6 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr"/>
       <c r="B93" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -14182,7 +13863,6 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr"/>
       <c r="B94" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -14225,7 +13905,6 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr"/>
       <c r="B95" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -14268,7 +13947,6 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr"/>
       <c r="B96" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -14311,7 +13989,6 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr"/>
       <c r="B97" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -14354,7 +14031,6 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr"/>
       <c r="B98" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -14397,7 +14073,6 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr"/>
       <c r="B99" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -14440,7 +14115,6 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr"/>
       <c r="B100" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -14483,7 +14157,6 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr"/>
       <c r="B101" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -14526,7 +14199,6 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr"/>
       <c r="B102" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -14569,7 +14241,6 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr"/>
       <c r="B103" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -14612,7 +14283,6 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr"/>
       <c r="B104" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -14655,7 +14325,6 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr"/>
       <c r="B105" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -14698,7 +14367,6 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr"/>
       <c r="B106" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -14741,7 +14409,6 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" t="inlineStr"/>
       <c r="B107" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -14784,7 +14451,6 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" t="inlineStr"/>
       <c r="B108" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -14827,7 +14493,6 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" t="inlineStr"/>
       <c r="B109" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -14870,7 +14535,6 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" t="inlineStr"/>
       <c r="B110" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -14913,7 +14577,6 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" t="inlineStr"/>
       <c r="B111" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -14956,7 +14619,6 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" t="inlineStr"/>
       <c r="B112" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -14999,7 +14661,6 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" t="inlineStr"/>
       <c r="B113" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -15042,7 +14703,6 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" t="inlineStr"/>
       <c r="B114" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -15085,7 +14745,6 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr"/>
       <c r="B115" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -15128,7 +14787,6 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" t="inlineStr"/>
       <c r="B116" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -15171,7 +14829,6 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" t="inlineStr"/>
       <c r="B117" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -15214,7 +14871,6 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" t="inlineStr"/>
       <c r="B118" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -15257,7 +14913,6 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" t="inlineStr"/>
       <c r="B119" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -15300,7 +14955,6 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" t="inlineStr"/>
       <c r="B120" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -15343,7 +14997,6 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" t="inlineStr"/>
       <c r="B121" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -15386,7 +15039,6 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="inlineStr"/>
       <c r="B122" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -15429,7 +15081,6 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" t="inlineStr"/>
       <c r="B123" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -15472,7 +15123,6 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" t="inlineStr"/>
       <c r="B124" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -15515,7 +15165,6 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" t="inlineStr"/>
       <c r="B125" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -15558,7 +15207,6 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" t="inlineStr"/>
       <c r="B126" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -15601,7 +15249,6 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" t="inlineStr"/>
       <c r="B127" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -15644,7 +15291,6 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" t="inlineStr"/>
       <c r="B128" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -15687,7 +15333,6 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" t="inlineStr"/>
       <c r="B129" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -15730,7 +15375,6 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" t="inlineStr"/>
       <c r="B130" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -15773,7 +15417,6 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" t="inlineStr"/>
       <c r="B131" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -15816,7 +15459,6 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" t="inlineStr"/>
       <c r="B132" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -15859,7 +15501,6 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" t="inlineStr"/>
       <c r="B133" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -15902,7 +15543,6 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" t="inlineStr"/>
       <c r="B134" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -15945,7 +15585,6 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" t="inlineStr"/>
       <c r="B135" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -15988,7 +15627,6 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" t="inlineStr"/>
       <c r="B136" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -16031,7 +15669,6 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" t="inlineStr"/>
       <c r="B137" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -16074,7 +15711,6 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" t="inlineStr"/>
       <c r="B138" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -16117,7 +15753,6 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" t="inlineStr"/>
       <c r="B139" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -16160,7 +15795,6 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" t="inlineStr"/>
       <c r="B140" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -16203,7 +15837,6 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" t="inlineStr"/>
       <c r="B141" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -16246,7 +15879,6 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" t="inlineStr"/>
       <c r="B142" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -16289,7 +15921,6 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" t="inlineStr"/>
       <c r="B143" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -16332,7 +15963,6 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" t="inlineStr"/>
       <c r="B144" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -16375,7 +16005,6 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" t="inlineStr"/>
       <c r="B145" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -16418,7 +16047,6 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" t="inlineStr"/>
       <c r="B146" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -16461,7 +16089,6 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" t="inlineStr"/>
       <c r="B147" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -16504,7 +16131,6 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" t="inlineStr"/>
       <c r="B148" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -16547,7 +16173,6 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" t="inlineStr"/>
       <c r="B149" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -16590,7 +16215,6 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" t="inlineStr"/>
       <c r="B150" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -16633,7 +16257,6 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" t="inlineStr"/>
       <c r="B151" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -16676,7 +16299,6 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" t="inlineStr"/>
       <c r="B152" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -16719,7 +16341,6 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" t="inlineStr"/>
       <c r="B153" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -16762,7 +16383,6 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" t="inlineStr"/>
       <c r="B154" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -16805,7 +16425,6 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" t="inlineStr"/>
       <c r="B155" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -16848,7 +16467,6 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" t="inlineStr"/>
       <c r="B156" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -16891,7 +16509,6 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" t="inlineStr"/>
       <c r="B157" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -16934,7 +16551,6 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" t="inlineStr"/>
       <c r="B158" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -16977,7 +16593,6 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" t="inlineStr"/>
       <c r="B159" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -17020,7 +16635,6 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" t="inlineStr"/>
       <c r="B160" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -17063,7 +16677,6 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" t="inlineStr"/>
       <c r="B161" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -17106,7 +16719,6 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" t="inlineStr"/>
       <c r="B162" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -17149,7 +16761,6 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" t="inlineStr"/>
       <c r="B163" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -17192,7 +16803,6 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" t="inlineStr"/>
       <c r="B164" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -17235,7 +16845,6 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" t="inlineStr"/>
       <c r="B165" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -17278,7 +16887,6 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" t="inlineStr"/>
       <c r="B166" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -17321,7 +16929,6 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" t="inlineStr"/>
       <c r="B167" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -17364,7 +16971,6 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" t="inlineStr"/>
       <c r="B168" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -17407,7 +17013,6 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" t="inlineStr"/>
       <c r="B169" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -17450,7 +17055,6 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" t="inlineStr"/>
       <c r="B170" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -17493,7 +17097,6 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" t="inlineStr"/>
       <c r="B171" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -17536,7 +17139,6 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" t="inlineStr"/>
       <c r="B172" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -17579,7 +17181,6 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" t="inlineStr"/>
       <c r="B173" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -17622,7 +17223,6 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" t="inlineStr"/>
       <c r="B174" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -17665,7 +17265,6 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" t="inlineStr"/>
       <c r="B175" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -17708,7 +17307,6 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" t="inlineStr"/>
       <c r="B176" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -17751,7 +17349,6 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" t="inlineStr"/>
       <c r="B177" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -17794,7 +17391,6 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" t="inlineStr"/>
       <c r="B178" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -17837,7 +17433,6 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" t="inlineStr"/>
       <c r="B179" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -17880,7 +17475,6 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" t="inlineStr"/>
       <c r="B180" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -17923,7 +17517,6 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" t="inlineStr"/>
       <c r="B181" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -17966,7 +17559,6 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" t="inlineStr"/>
       <c r="B182" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -18009,7 +17601,6 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" t="inlineStr"/>
       <c r="B183" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -18052,7 +17643,6 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" t="inlineStr"/>
       <c r="B184" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -18095,7 +17685,6 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" t="inlineStr"/>
       <c r="B185" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -18138,7 +17727,6 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" t="inlineStr"/>
       <c r="B186" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -18181,7 +17769,6 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" t="inlineStr"/>
       <c r="B187" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -18224,7 +17811,6 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" t="inlineStr"/>
       <c r="B188" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -18267,7 +17853,6 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" t="inlineStr"/>
       <c r="B189" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -18310,7 +17895,6 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" t="inlineStr"/>
       <c r="B190" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -18353,7 +17937,6 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" t="inlineStr"/>
       <c r="B191" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -18396,7 +17979,6 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" t="inlineStr"/>
       <c r="B192" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -18439,7 +18021,6 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" t="inlineStr"/>
       <c r="B193" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -18482,7 +18063,6 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" t="inlineStr"/>
       <c r="B194" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -18525,7 +18105,6 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" t="inlineStr"/>
       <c r="B195" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -18568,7 +18147,6 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" t="inlineStr"/>
       <c r="B196" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -18611,7 +18189,6 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" t="inlineStr"/>
       <c r="B197" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -18654,7 +18231,6 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" t="inlineStr"/>
       <c r="B198" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -18697,7 +18273,6 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" t="inlineStr"/>
       <c r="B199" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -18740,7 +18315,6 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" t="inlineStr"/>
       <c r="B200" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -18783,7 +18357,6 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" t="inlineStr"/>
       <c r="B201" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -18826,7 +18399,6 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" t="inlineStr"/>
       <c r="B202" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -18869,7 +18441,6 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" t="inlineStr"/>
       <c r="B203" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -18912,7 +18483,6 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" t="inlineStr"/>
       <c r="B204" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -18955,7 +18525,6 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" t="inlineStr"/>
       <c r="B205" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -18998,7 +18567,6 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" t="inlineStr"/>
       <c r="B206" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -19041,7 +18609,6 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" t="inlineStr"/>
       <c r="B207" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -19084,7 +18651,6 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" t="inlineStr"/>
       <c r="B208" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa II)</t>
@@ -19127,7 +18693,6 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" t="inlineStr"/>
       <c r="B209" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa II)</t>
@@ -19170,7 +18735,6 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" t="inlineStr"/>
       <c r="B210" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa II)</t>
@@ -19213,7 +18777,6 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" t="inlineStr"/>
       <c r="B211" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa II)</t>
@@ -19256,7 +18819,6 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" t="inlineStr"/>
       <c r="B212" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa II)</t>
@@ -19299,7 +18861,6 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" t="inlineStr"/>
       <c r="B213" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa II)</t>
@@ -19342,7 +18903,6 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" t="inlineStr"/>
       <c r="B214" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa II)</t>
@@ -19385,7 +18945,6 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" t="inlineStr"/>
       <c r="B215" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa II)</t>
@@ -19428,7 +18987,6 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" t="inlineStr"/>
       <c r="B216" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa II)</t>
@@ -19471,7 +19029,6 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" t="inlineStr"/>
       <c r="B217" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa II)</t>
@@ -19514,7 +19071,6 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" t="inlineStr"/>
       <c r="B218" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa II)</t>
@@ -19557,7 +19113,6 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" t="inlineStr"/>
       <c r="B219" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa II)</t>
@@ -19600,7 +19155,6 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" t="inlineStr"/>
       <c r="B220" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa II)</t>
@@ -19643,7 +19197,6 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" t="inlineStr"/>
       <c r="B221" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa II)</t>
@@ -19686,7 +19239,6 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" t="inlineStr"/>
       <c r="B222" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa II)</t>
@@ -19729,7 +19281,6 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" t="inlineStr"/>
       <c r="B223" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa II)</t>
@@ -19760,19 +19311,18 @@
           <t>0.013%</t>
         </is>
       </c>
-      <c r="H223" s="2" t="inlineStr">
+      <c r="H223" s="3" t="inlineStr">
         <is>
           <t>280-21XXXX</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>AMBIGUA: revisar manualmente opciones 280-226117, 280-226125</t>
+          <t>AMBIGUA: revisar 280-226117, 280-226125</t>
         </is>
       </c>
     </row>
     <row r="224">
-      <c r="A224" t="inlineStr"/>
       <c r="B224" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa II)</t>
@@ -19815,7 +19365,6 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" t="inlineStr"/>
       <c r="B225" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa II)</t>
@@ -19858,7 +19407,6 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" t="inlineStr"/>
       <c r="B226" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa II)</t>
@@ -19901,7 +19449,6 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" t="inlineStr"/>
       <c r="B227" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa II)</t>
@@ -19944,7 +19491,6 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" t="inlineStr"/>
       <c r="B228" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa II)</t>
@@ -19987,7 +19533,6 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" t="inlineStr"/>
       <c r="B229" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa II)</t>
@@ -20030,7 +19575,6 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" t="inlineStr"/>
       <c r="B230" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa II)</t>
@@ -20073,7 +19617,6 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" t="inlineStr"/>
       <c r="B231" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa II)</t>
@@ -20116,7 +19659,6 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" t="inlineStr"/>
       <c r="B232" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa II)</t>
@@ -20159,7 +19701,6 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" t="inlineStr"/>
       <c r="B233" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa II)</t>
@@ -20202,7 +19743,6 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" t="inlineStr"/>
       <c r="B234" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa II)</t>
@@ -20245,7 +19785,6 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" t="inlineStr"/>
       <c r="B235" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa II)</t>
@@ -20288,7 +19827,6 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" t="inlineStr"/>
       <c r="B236" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa II)</t>
@@ -20331,7 +19869,6 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" t="inlineStr"/>
       <c r="B237" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa II)</t>
@@ -20374,7 +19911,6 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" t="inlineStr"/>
       <c r="B238" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa II)</t>
@@ -20417,7 +19953,6 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" t="inlineStr"/>
       <c r="B239" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa II)</t>
@@ -20460,14 +19995,11 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" t="inlineStr"/>
       <c r="B240" t="inlineStr">
         <is>
           <t>TOTAL PARQUEADEROS (234)</t>
         </is>
       </c>
-      <c r="C240" t="inlineStr"/>
-      <c r="D240" t="inlineStr"/>
       <c r="E240" t="inlineStr">
         <is>
           <t>1,287.40</t>
@@ -20505,7 +20037,6 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
           <t>SANTA SOFÍA CLUB RESIDENCIAL</t>
@@ -20513,7 +20044,6 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
           <t>SISTEMA DE CONTROL Y REGISTRO DE MATRÍCULAS INMOBILIARIAS</t>
@@ -20521,7 +20051,6 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
           <t>Generated Sep 2026 | v1.0 | Base de datos master de la copropiedad</t>
@@ -20529,7 +20058,6 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
           <t>RANGOS OFICIALES DE MATRÍCULAS INMOBILIARIAS (SEGÚN ESCRITURAS)</t>
@@ -20537,7 +20065,6 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
           <t>Etapa</t>
@@ -20565,7 +20092,6 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
           <t>Etapa I (Fase 1)</t>
@@ -20593,7 +20119,6 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
           <t>Etapa II (Fase 2)</t>
@@ -20621,7 +20146,6 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
           <t>CONVENCIÓN DE COLORES PARA LA ADMINISTRACIÓN</t>
@@ -20629,7 +20153,6 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
           <t>Celda de Entrada (Light Blue)</t>
@@ -20642,7 +20165,6 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
           <t>Celda Calculada (Light Green)</t>
@@ -20655,7 +20177,6 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
           <t>ESTADÍSTICAS GENERALES DE UNIDADES PRIVADAS</t>
@@ -20663,7 +20184,6 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
           <t>Tipo de Unidad</t>
@@ -20691,7 +20211,6 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
           <t>Apartamentos Torre 1 (Bloques 1, 2, 3 y 4)</t>
@@ -20719,7 +20238,6 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
           <t>Parqueaderos de Carros Privados</t>
@@ -20747,7 +20265,6 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
           <t>Parqueaderos de Motos Privados</t>
@@ -20775,7 +20292,6 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
           <t>Gran Total Copropiedad</t>

--- a/data/matriculas_santa_sofia_OFICIAL.xlsx
+++ b/data/matriculas_santa_sofia_OFICIAL.xlsx
@@ -28,7 +28,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -45,11 +45,6 @@
         <fgColor rgb="00F4CCCC"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -63,11 +58,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -437,6 +431,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
+      <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
           <t>BASE DE DATOS DE APARTAMENTOS Y REGISTRO DE MATRÍCULAS</t>
@@ -444,6 +439,7 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
           <t>Nota: Los coeficientes están actualizados según la Adición por Etapas de la Ley 675.</t>
@@ -451,6 +447,7 @@
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
           <t>Bloque</t>
@@ -493,6 +490,7 @@
       </c>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -535,6 +533,7 @@
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -577,6 +576,7 @@
       </c>
     </row>
     <row r="8">
+      <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -619,6 +619,7 @@
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -661,6 +662,7 @@
       </c>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -703,6 +705,7 @@
       </c>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -745,6 +748,7 @@
       </c>
     </row>
     <row r="12">
+      <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -787,6 +791,7 @@
       </c>
     </row>
     <row r="13">
+      <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -829,6 +834,7 @@
       </c>
     </row>
     <row r="14">
+      <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -871,6 +877,7 @@
       </c>
     </row>
     <row r="15">
+      <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -913,6 +920,7 @@
       </c>
     </row>
     <row r="16">
+      <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -955,6 +963,7 @@
       </c>
     </row>
     <row r="17">
+      <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -997,6 +1006,7 @@
       </c>
     </row>
     <row r="18">
+      <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -1039,6 +1049,7 @@
       </c>
     </row>
     <row r="19">
+      <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -1081,6 +1092,7 @@
       </c>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -1123,6 +1135,7 @@
       </c>
     </row>
     <row r="21">
+      <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -1165,6 +1178,7 @@
       </c>
     </row>
     <row r="22">
+      <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -1207,6 +1221,7 @@
       </c>
     </row>
     <row r="23">
+      <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -1249,6 +1264,7 @@
       </c>
     </row>
     <row r="24">
+      <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -1291,6 +1307,7 @@
       </c>
     </row>
     <row r="25">
+      <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -1333,6 +1350,7 @@
       </c>
     </row>
     <row r="26">
+      <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -1375,6 +1393,7 @@
       </c>
     </row>
     <row r="27">
+      <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -1417,6 +1436,7 @@
       </c>
     </row>
     <row r="28">
+      <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -1459,6 +1479,7 @@
       </c>
     </row>
     <row r="29">
+      <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -1501,6 +1522,7 @@
       </c>
     </row>
     <row r="30">
+      <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -1543,6 +1565,7 @@
       </c>
     </row>
     <row r="31">
+      <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -1585,6 +1608,7 @@
       </c>
     </row>
     <row r="32">
+      <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -1627,6 +1651,7 @@
       </c>
     </row>
     <row r="33">
+      <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -1669,6 +1694,7 @@
       </c>
     </row>
     <row r="34">
+      <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -1711,6 +1737,7 @@
       </c>
     </row>
     <row r="35">
+      <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -1753,6 +1780,7 @@
       </c>
     </row>
     <row r="36">
+      <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -1795,6 +1823,7 @@
       </c>
     </row>
     <row r="37">
+      <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -1837,6 +1866,7 @@
       </c>
     </row>
     <row r="38">
+      <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -1879,6 +1909,7 @@
       </c>
     </row>
     <row r="39">
+      <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -1921,6 +1952,7 @@
       </c>
     </row>
     <row r="40">
+      <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -1963,6 +1995,7 @@
       </c>
     </row>
     <row r="41">
+      <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -2005,6 +2038,7 @@
       </c>
     </row>
     <row r="42">
+      <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -2047,6 +2081,7 @@
       </c>
     </row>
     <row r="43">
+      <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -2089,6 +2124,7 @@
       </c>
     </row>
     <row r="44">
+      <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -2131,6 +2167,7 @@
       </c>
     </row>
     <row r="45">
+      <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -2173,6 +2210,7 @@
       </c>
     </row>
     <row r="46">
+      <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -2215,6 +2253,7 @@
       </c>
     </row>
     <row r="47">
+      <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -2257,6 +2296,7 @@
       </c>
     </row>
     <row r="48">
+      <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -2299,6 +2339,7 @@
       </c>
     </row>
     <row r="49">
+      <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -2341,6 +2382,7 @@
       </c>
     </row>
     <row r="50">
+      <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -2383,6 +2425,7 @@
       </c>
     </row>
     <row r="51">
+      <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -2425,6 +2468,7 @@
       </c>
     </row>
     <row r="52">
+      <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -2467,6 +2511,7 @@
       </c>
     </row>
     <row r="53">
+      <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -2509,6 +2554,7 @@
       </c>
     </row>
     <row r="54">
+      <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -2551,6 +2597,7 @@
       </c>
     </row>
     <row r="55">
+      <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -2593,6 +2640,7 @@
       </c>
     </row>
     <row r="56">
+      <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -2635,6 +2683,7 @@
       </c>
     </row>
     <row r="57">
+      <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -2677,6 +2726,7 @@
       </c>
     </row>
     <row r="58">
+      <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -2719,6 +2769,7 @@
       </c>
     </row>
     <row r="59">
+      <c r="A59" t="inlineStr"/>
       <c r="B59" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -2761,6 +2812,7 @@
       </c>
     </row>
     <row r="60">
+      <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -2803,6 +2855,7 @@
       </c>
     </row>
     <row r="61">
+      <c r="A61" t="inlineStr"/>
       <c r="B61" t="inlineStr">
         <is>
           <t>Bloque 3</t>
@@ -2845,6 +2898,7 @@
       </c>
     </row>
     <row r="62">
+      <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -2887,6 +2941,7 @@
       </c>
     </row>
     <row r="63">
+      <c r="A63" t="inlineStr"/>
       <c r="B63" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -2929,6 +2984,7 @@
       </c>
     </row>
     <row r="64">
+      <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -2971,6 +3027,7 @@
       </c>
     </row>
     <row r="65">
+      <c r="A65" t="inlineStr"/>
       <c r="B65" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -3013,6 +3070,7 @@
       </c>
     </row>
     <row r="66">
+      <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -3055,6 +3113,7 @@
       </c>
     </row>
     <row r="67">
+      <c r="A67" t="inlineStr"/>
       <c r="B67" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -3097,6 +3156,7 @@
       </c>
     </row>
     <row r="68">
+      <c r="A68" t="inlineStr"/>
       <c r="B68" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -3139,6 +3199,7 @@
       </c>
     </row>
     <row r="69">
+      <c r="A69" t="inlineStr"/>
       <c r="B69" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -3181,6 +3242,7 @@
       </c>
     </row>
     <row r="70">
+      <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -3223,6 +3285,7 @@
       </c>
     </row>
     <row r="71">
+      <c r="A71" t="inlineStr"/>
       <c r="B71" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -3265,6 +3328,7 @@
       </c>
     </row>
     <row r="72">
+      <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -3307,6 +3371,7 @@
       </c>
     </row>
     <row r="73">
+      <c r="A73" t="inlineStr"/>
       <c r="B73" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -3349,6 +3414,7 @@
       </c>
     </row>
     <row r="74">
+      <c r="A74" t="inlineStr"/>
       <c r="B74" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -3391,6 +3457,7 @@
       </c>
     </row>
     <row r="75">
+      <c r="A75" t="inlineStr"/>
       <c r="B75" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -3433,6 +3500,7 @@
       </c>
     </row>
     <row r="76">
+      <c r="A76" t="inlineStr"/>
       <c r="B76" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -3475,6 +3543,7 @@
       </c>
     </row>
     <row r="77">
+      <c r="A77" t="inlineStr"/>
       <c r="B77" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -3517,6 +3586,7 @@
       </c>
     </row>
     <row r="78">
+      <c r="A78" t="inlineStr"/>
       <c r="B78" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -3559,6 +3629,7 @@
       </c>
     </row>
     <row r="79">
+      <c r="A79" t="inlineStr"/>
       <c r="B79" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -3601,6 +3672,7 @@
       </c>
     </row>
     <row r="80">
+      <c r="A80" t="inlineStr"/>
       <c r="B80" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -3643,6 +3715,7 @@
       </c>
     </row>
     <row r="81">
+      <c r="A81" t="inlineStr"/>
       <c r="B81" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -3685,6 +3758,7 @@
       </c>
     </row>
     <row r="82">
+      <c r="A82" t="inlineStr"/>
       <c r="B82" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -3727,6 +3801,7 @@
       </c>
     </row>
     <row r="83">
+      <c r="A83" t="inlineStr"/>
       <c r="B83" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -3769,6 +3844,7 @@
       </c>
     </row>
     <row r="84">
+      <c r="A84" t="inlineStr"/>
       <c r="B84" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -3811,6 +3887,7 @@
       </c>
     </row>
     <row r="85">
+      <c r="A85" t="inlineStr"/>
       <c r="B85" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -3853,6 +3930,7 @@
       </c>
     </row>
     <row r="86">
+      <c r="A86" t="inlineStr"/>
       <c r="B86" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -3895,6 +3973,7 @@
       </c>
     </row>
     <row r="87">
+      <c r="A87" t="inlineStr"/>
       <c r="B87" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -3937,6 +4016,7 @@
       </c>
     </row>
     <row r="88">
+      <c r="A88" t="inlineStr"/>
       <c r="B88" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -3979,6 +4059,7 @@
       </c>
     </row>
     <row r="89">
+      <c r="A89" t="inlineStr"/>
       <c r="B89" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -4021,6 +4102,7 @@
       </c>
     </row>
     <row r="90">
+      <c r="A90" t="inlineStr"/>
       <c r="B90" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -4063,6 +4145,7 @@
       </c>
     </row>
     <row r="91">
+      <c r="A91" t="inlineStr"/>
       <c r="B91" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -4105,6 +4188,7 @@
       </c>
     </row>
     <row r="92">
+      <c r="A92" t="inlineStr"/>
       <c r="B92" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -4147,6 +4231,7 @@
       </c>
     </row>
     <row r="93">
+      <c r="A93" t="inlineStr"/>
       <c r="B93" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -4189,6 +4274,7 @@
       </c>
     </row>
     <row r="94">
+      <c r="A94" t="inlineStr"/>
       <c r="B94" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -4231,6 +4317,7 @@
       </c>
     </row>
     <row r="95">
+      <c r="A95" t="inlineStr"/>
       <c r="B95" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -4273,6 +4360,7 @@
       </c>
     </row>
     <row r="96">
+      <c r="A96" t="inlineStr"/>
       <c r="B96" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -4315,6 +4403,7 @@
       </c>
     </row>
     <row r="97">
+      <c r="A97" t="inlineStr"/>
       <c r="B97" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -4357,6 +4446,7 @@
       </c>
     </row>
     <row r="98">
+      <c r="A98" t="inlineStr"/>
       <c r="B98" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -4399,6 +4489,7 @@
       </c>
     </row>
     <row r="99">
+      <c r="A99" t="inlineStr"/>
       <c r="B99" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -4441,6 +4532,7 @@
       </c>
     </row>
     <row r="100">
+      <c r="A100" t="inlineStr"/>
       <c r="B100" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -4483,6 +4575,7 @@
       </c>
     </row>
     <row r="101">
+      <c r="A101" t="inlineStr"/>
       <c r="B101" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -4525,6 +4618,7 @@
       </c>
     </row>
     <row r="102">
+      <c r="A102" t="inlineStr"/>
       <c r="B102" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -4567,6 +4661,7 @@
       </c>
     </row>
     <row r="103">
+      <c r="A103" t="inlineStr"/>
       <c r="B103" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -4609,6 +4704,7 @@
       </c>
     </row>
     <row r="104">
+      <c r="A104" t="inlineStr"/>
       <c r="B104" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -4651,6 +4747,7 @@
       </c>
     </row>
     <row r="105">
+      <c r="A105" t="inlineStr"/>
       <c r="B105" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -4693,6 +4790,7 @@
       </c>
     </row>
     <row r="106">
+      <c r="A106" t="inlineStr"/>
       <c r="B106" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -4735,6 +4833,7 @@
       </c>
     </row>
     <row r="107">
+      <c r="A107" t="inlineStr"/>
       <c r="B107" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -4777,6 +4876,7 @@
       </c>
     </row>
     <row r="108">
+      <c r="A108" t="inlineStr"/>
       <c r="B108" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -4819,6 +4919,7 @@
       </c>
     </row>
     <row r="109">
+      <c r="A109" t="inlineStr"/>
       <c r="B109" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -4861,6 +4962,7 @@
       </c>
     </row>
     <row r="110">
+      <c r="A110" t="inlineStr"/>
       <c r="B110" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -4903,6 +5005,7 @@
       </c>
     </row>
     <row r="111">
+      <c r="A111" t="inlineStr"/>
       <c r="B111" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -4945,6 +5048,7 @@
       </c>
     </row>
     <row r="112">
+      <c r="A112" t="inlineStr"/>
       <c r="B112" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -4987,6 +5091,7 @@
       </c>
     </row>
     <row r="113">
+      <c r="A113" t="inlineStr"/>
       <c r="B113" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -5029,6 +5134,7 @@
       </c>
     </row>
     <row r="114">
+      <c r="A114" t="inlineStr"/>
       <c r="B114" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -5071,6 +5177,7 @@
       </c>
     </row>
     <row r="115">
+      <c r="A115" t="inlineStr"/>
       <c r="B115" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -5113,6 +5220,7 @@
       </c>
     </row>
     <row r="116">
+      <c r="A116" t="inlineStr"/>
       <c r="B116" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -5155,6 +5263,7 @@
       </c>
     </row>
     <row r="117">
+      <c r="A117" t="inlineStr"/>
       <c r="B117" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -5197,6 +5306,7 @@
       </c>
     </row>
     <row r="118">
+      <c r="A118" t="inlineStr"/>
       <c r="B118" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -5239,6 +5349,7 @@
       </c>
     </row>
     <row r="119">
+      <c r="A119" t="inlineStr"/>
       <c r="B119" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -5281,6 +5392,7 @@
       </c>
     </row>
     <row r="120">
+      <c r="A120" t="inlineStr"/>
       <c r="B120" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -5323,6 +5435,7 @@
       </c>
     </row>
     <row r="121">
+      <c r="A121" t="inlineStr"/>
       <c r="B121" t="inlineStr">
         <is>
           <t>Bloque 4</t>
@@ -5365,6 +5478,7 @@
       </c>
     </row>
     <row r="122">
+      <c r="A122" t="inlineStr"/>
       <c r="B122" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -5395,9 +5509,9 @@
           <t>0.408%</t>
         </is>
       </c>
-      <c r="H122" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H122" s="1" t="inlineStr">
+        <is>
+          <t>280-225990</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -5407,6 +5521,7 @@
       </c>
     </row>
     <row r="123">
+      <c r="A123" t="inlineStr"/>
       <c r="B123" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -5437,9 +5552,9 @@
           <t>0.465%</t>
         </is>
       </c>
-      <c r="H123" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H123" s="1" t="inlineStr">
+        <is>
+          <t>280-225991</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -5449,6 +5564,7 @@
       </c>
     </row>
     <row r="124">
+      <c r="A124" t="inlineStr"/>
       <c r="B124" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -5479,9 +5595,9 @@
           <t>0.465%</t>
         </is>
       </c>
-      <c r="H124" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H124" s="1" t="inlineStr">
+        <is>
+          <t>280-225992</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -5491,6 +5607,7 @@
       </c>
     </row>
     <row r="125">
+      <c r="A125" t="inlineStr"/>
       <c r="B125" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -5521,9 +5638,9 @@
           <t>0.408%</t>
         </is>
       </c>
-      <c r="H125" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H125" s="1" t="inlineStr">
+        <is>
+          <t>280-225993</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -5533,6 +5650,7 @@
       </c>
     </row>
     <row r="126">
+      <c r="A126" t="inlineStr"/>
       <c r="B126" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -5563,9 +5681,9 @@
           <t>0.408%</t>
         </is>
       </c>
-      <c r="H126" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H126" s="1" t="inlineStr">
+        <is>
+          <t>280-225994</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -5575,6 +5693,7 @@
       </c>
     </row>
     <row r="127">
+      <c r="A127" t="inlineStr"/>
       <c r="B127" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -5605,9 +5724,9 @@
           <t>0.465%</t>
         </is>
       </c>
-      <c r="H127" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H127" s="1" t="inlineStr">
+        <is>
+          <t>280-225995</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -5617,6 +5736,7 @@
       </c>
     </row>
     <row r="128">
+      <c r="A128" t="inlineStr"/>
       <c r="B128" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -5647,9 +5767,9 @@
           <t>0.465%</t>
         </is>
       </c>
-      <c r="H128" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H128" s="1" t="inlineStr">
+        <is>
+          <t>280-225996</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -5659,6 +5779,7 @@
       </c>
     </row>
     <row r="129">
+      <c r="A129" t="inlineStr"/>
       <c r="B129" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -5689,9 +5810,9 @@
           <t>0.408%</t>
         </is>
       </c>
-      <c r="H129" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H129" s="1" t="inlineStr">
+        <is>
+          <t>280-225997</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -5701,6 +5822,7 @@
       </c>
     </row>
     <row r="130">
+      <c r="A130" t="inlineStr"/>
       <c r="B130" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -5731,9 +5853,9 @@
           <t>0.408%</t>
         </is>
       </c>
-      <c r="H130" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H130" s="1" t="inlineStr">
+        <is>
+          <t>280-225998</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -5743,6 +5865,7 @@
       </c>
     </row>
     <row r="131">
+      <c r="A131" t="inlineStr"/>
       <c r="B131" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -5773,9 +5896,9 @@
           <t>0.465%</t>
         </is>
       </c>
-      <c r="H131" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H131" s="1" t="inlineStr">
+        <is>
+          <t>280-225999</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -5785,6 +5908,7 @@
       </c>
     </row>
     <row r="132">
+      <c r="A132" t="inlineStr"/>
       <c r="B132" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -5815,9 +5939,9 @@
           <t>0.465%</t>
         </is>
       </c>
-      <c r="H132" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H132" s="1" t="inlineStr">
+        <is>
+          <t>280-226000</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -5827,6 +5951,7 @@
       </c>
     </row>
     <row r="133">
+      <c r="A133" t="inlineStr"/>
       <c r="B133" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -5857,9 +5982,9 @@
           <t>0.408%</t>
         </is>
       </c>
-      <c r="H133" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H133" s="1" t="inlineStr">
+        <is>
+          <t>280-226001</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -5869,6 +5994,7 @@
       </c>
     </row>
     <row r="134">
+      <c r="A134" t="inlineStr"/>
       <c r="B134" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -5899,9 +6025,9 @@
           <t>0.408%</t>
         </is>
       </c>
-      <c r="H134" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H134" s="1" t="inlineStr">
+        <is>
+          <t>280-226002</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -5911,6 +6037,7 @@
       </c>
     </row>
     <row r="135">
+      <c r="A135" t="inlineStr"/>
       <c r="B135" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -5941,9 +6068,9 @@
           <t>0.465%</t>
         </is>
       </c>
-      <c r="H135" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H135" s="1" t="inlineStr">
+        <is>
+          <t>280-226003</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -5953,6 +6080,7 @@
       </c>
     </row>
     <row r="136">
+      <c r="A136" t="inlineStr"/>
       <c r="B136" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -5983,9 +6111,9 @@
           <t>0.465%</t>
         </is>
       </c>
-      <c r="H136" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H136" s="1" t="inlineStr">
+        <is>
+          <t>280-226004</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -5995,6 +6123,7 @@
       </c>
     </row>
     <row r="137">
+      <c r="A137" t="inlineStr"/>
       <c r="B137" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -6025,9 +6154,9 @@
           <t>0.408%</t>
         </is>
       </c>
-      <c r="H137" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H137" s="1" t="inlineStr">
+        <is>
+          <t>280-226005</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -6037,6 +6166,7 @@
       </c>
     </row>
     <row r="138">
+      <c r="A138" t="inlineStr"/>
       <c r="B138" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -6067,9 +6197,9 @@
           <t>0.408%</t>
         </is>
       </c>
-      <c r="H138" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H138" s="1" t="inlineStr">
+        <is>
+          <t>280-226006</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -6079,6 +6209,7 @@
       </c>
     </row>
     <row r="139">
+      <c r="A139" t="inlineStr"/>
       <c r="B139" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -6109,9 +6240,9 @@
           <t>0.465%</t>
         </is>
       </c>
-      <c r="H139" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H139" s="1" t="inlineStr">
+        <is>
+          <t>280-226007</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -6121,6 +6252,7 @@
       </c>
     </row>
     <row r="140">
+      <c r="A140" t="inlineStr"/>
       <c r="B140" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -6151,9 +6283,9 @@
           <t>0.465%</t>
         </is>
       </c>
-      <c r="H140" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H140" s="1" t="inlineStr">
+        <is>
+          <t>280-226008</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -6163,6 +6295,7 @@
       </c>
     </row>
     <row r="141">
+      <c r="A141" t="inlineStr"/>
       <c r="B141" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -6193,9 +6326,9 @@
           <t>0.408%</t>
         </is>
       </c>
-      <c r="H141" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H141" s="1" t="inlineStr">
+        <is>
+          <t>280-226009</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -6205,6 +6338,7 @@
       </c>
     </row>
     <row r="142">
+      <c r="A142" t="inlineStr"/>
       <c r="B142" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -6235,9 +6369,9 @@
           <t>0.408%</t>
         </is>
       </c>
-      <c r="H142" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H142" s="1" t="inlineStr">
+        <is>
+          <t>280-226010</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -6247,6 +6381,7 @@
       </c>
     </row>
     <row r="143">
+      <c r="A143" t="inlineStr"/>
       <c r="B143" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -6277,9 +6412,9 @@
           <t>0.465%</t>
         </is>
       </c>
-      <c r="H143" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H143" s="1" t="inlineStr">
+        <is>
+          <t>280-226011</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -6289,6 +6424,7 @@
       </c>
     </row>
     <row r="144">
+      <c r="A144" t="inlineStr"/>
       <c r="B144" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -6319,9 +6455,9 @@
           <t>0.465%</t>
         </is>
       </c>
-      <c r="H144" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H144" s="1" t="inlineStr">
+        <is>
+          <t>280-226012</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -6331,6 +6467,7 @@
       </c>
     </row>
     <row r="145">
+      <c r="A145" t="inlineStr"/>
       <c r="B145" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -6361,9 +6498,9 @@
           <t>0.408%</t>
         </is>
       </c>
-      <c r="H145" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H145" s="1" t="inlineStr">
+        <is>
+          <t>280-226013</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -6373,6 +6510,7 @@
       </c>
     </row>
     <row r="146">
+      <c r="A146" t="inlineStr"/>
       <c r="B146" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -6403,9 +6541,9 @@
           <t>0.408%</t>
         </is>
       </c>
-      <c r="H146" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H146" s="1" t="inlineStr">
+        <is>
+          <t>280-226014</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -6415,6 +6553,7 @@
       </c>
     </row>
     <row r="147">
+      <c r="A147" t="inlineStr"/>
       <c r="B147" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -6445,9 +6584,9 @@
           <t>0.465%</t>
         </is>
       </c>
-      <c r="H147" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H147" s="1" t="inlineStr">
+        <is>
+          <t>280-226015</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -6457,6 +6596,7 @@
       </c>
     </row>
     <row r="148">
+      <c r="A148" t="inlineStr"/>
       <c r="B148" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -6487,9 +6627,9 @@
           <t>0.465%</t>
         </is>
       </c>
-      <c r="H148" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H148" s="1" t="inlineStr">
+        <is>
+          <t>280-226016</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -6499,6 +6639,7 @@
       </c>
     </row>
     <row r="149">
+      <c r="A149" t="inlineStr"/>
       <c r="B149" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -6529,9 +6670,9 @@
           <t>0.408%</t>
         </is>
       </c>
-      <c r="H149" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H149" s="1" t="inlineStr">
+        <is>
+          <t>280-226017</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -6541,6 +6682,7 @@
       </c>
     </row>
     <row r="150">
+      <c r="A150" t="inlineStr"/>
       <c r="B150" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -6571,9 +6713,9 @@
           <t>0.408%</t>
         </is>
       </c>
-      <c r="H150" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H150" s="1" t="inlineStr">
+        <is>
+          <t>280-226018</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -6583,6 +6725,7 @@
       </c>
     </row>
     <row r="151">
+      <c r="A151" t="inlineStr"/>
       <c r="B151" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -6613,9 +6756,9 @@
           <t>0.465%</t>
         </is>
       </c>
-      <c r="H151" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H151" s="1" t="inlineStr">
+        <is>
+          <t>280-226019</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -6625,6 +6768,7 @@
       </c>
     </row>
     <row r="152">
+      <c r="A152" t="inlineStr"/>
       <c r="B152" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -6655,9 +6799,9 @@
           <t>0.465%</t>
         </is>
       </c>
-      <c r="H152" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H152" s="1" t="inlineStr">
+        <is>
+          <t>280-226020</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -6667,6 +6811,7 @@
       </c>
     </row>
     <row r="153">
+      <c r="A153" t="inlineStr"/>
       <c r="B153" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -6697,9 +6842,9 @@
           <t>0.408%</t>
         </is>
       </c>
-      <c r="H153" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H153" s="1" t="inlineStr">
+        <is>
+          <t>280-226021</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -6709,6 +6854,7 @@
       </c>
     </row>
     <row r="154">
+      <c r="A154" t="inlineStr"/>
       <c r="B154" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -6739,9 +6885,9 @@
           <t>0.408%</t>
         </is>
       </c>
-      <c r="H154" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H154" s="1" t="inlineStr">
+        <is>
+          <t>280-226022</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -6751,6 +6897,7 @@
       </c>
     </row>
     <row r="155">
+      <c r="A155" t="inlineStr"/>
       <c r="B155" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -6781,9 +6928,9 @@
           <t>0.465%</t>
         </is>
       </c>
-      <c r="H155" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H155" s="1" t="inlineStr">
+        <is>
+          <t>280-226023</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -6793,6 +6940,7 @@
       </c>
     </row>
     <row r="156">
+      <c r="A156" t="inlineStr"/>
       <c r="B156" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -6823,9 +6971,9 @@
           <t>0.465%</t>
         </is>
       </c>
-      <c r="H156" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H156" s="1" t="inlineStr">
+        <is>
+          <t>280-226024</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -6835,6 +6983,7 @@
       </c>
     </row>
     <row r="157">
+      <c r="A157" t="inlineStr"/>
       <c r="B157" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -6865,9 +7014,9 @@
           <t>0.408%</t>
         </is>
       </c>
-      <c r="H157" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H157" s="1" t="inlineStr">
+        <is>
+          <t>280-226025</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -6877,6 +7026,7 @@
       </c>
     </row>
     <row r="158">
+      <c r="A158" t="inlineStr"/>
       <c r="B158" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -6907,9 +7057,9 @@
           <t>0.408%</t>
         </is>
       </c>
-      <c r="H158" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H158" s="1" t="inlineStr">
+        <is>
+          <t>280-226026</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -6919,6 +7069,7 @@
       </c>
     </row>
     <row r="159">
+      <c r="A159" t="inlineStr"/>
       <c r="B159" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -6949,9 +7100,9 @@
           <t>0.465%</t>
         </is>
       </c>
-      <c r="H159" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H159" s="1" t="inlineStr">
+        <is>
+          <t>280-226027</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -6961,6 +7112,7 @@
       </c>
     </row>
     <row r="160">
+      <c r="A160" t="inlineStr"/>
       <c r="B160" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -6991,9 +7143,9 @@
           <t>0.465%</t>
         </is>
       </c>
-      <c r="H160" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H160" s="1" t="inlineStr">
+        <is>
+          <t>280-226028</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -7003,6 +7155,7 @@
       </c>
     </row>
     <row r="161">
+      <c r="A161" t="inlineStr"/>
       <c r="B161" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -7033,9 +7186,9 @@
           <t>0.408%</t>
         </is>
       </c>
-      <c r="H161" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H161" s="1" t="inlineStr">
+        <is>
+          <t>280-226029</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -7045,6 +7198,7 @@
       </c>
     </row>
     <row r="162">
+      <c r="A162" t="inlineStr"/>
       <c r="B162" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -7075,9 +7229,9 @@
           <t>0.408%</t>
         </is>
       </c>
-      <c r="H162" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H162" s="1" t="inlineStr">
+        <is>
+          <t>280-226030</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -7087,6 +7241,7 @@
       </c>
     </row>
     <row r="163">
+      <c r="A163" t="inlineStr"/>
       <c r="B163" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -7117,9 +7272,9 @@
           <t>0.465%</t>
         </is>
       </c>
-      <c r="H163" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H163" s="1" t="inlineStr">
+        <is>
+          <t>280-226031</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -7129,6 +7284,7 @@
       </c>
     </row>
     <row r="164">
+      <c r="A164" t="inlineStr"/>
       <c r="B164" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -7159,9 +7315,9 @@
           <t>0.465%</t>
         </is>
       </c>
-      <c r="H164" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H164" s="1" t="inlineStr">
+        <is>
+          <t>280-226032</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -7171,6 +7327,7 @@
       </c>
     </row>
     <row r="165">
+      <c r="A165" t="inlineStr"/>
       <c r="B165" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -7201,9 +7358,9 @@
           <t>0.408%</t>
         </is>
       </c>
-      <c r="H165" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H165" s="1" t="inlineStr">
+        <is>
+          <t>280-226033</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -7213,6 +7370,7 @@
       </c>
     </row>
     <row r="166">
+      <c r="A166" t="inlineStr"/>
       <c r="B166" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -7243,9 +7401,9 @@
           <t>0.408%</t>
         </is>
       </c>
-      <c r="H166" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H166" s="1" t="inlineStr">
+        <is>
+          <t>280-226034</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -7255,6 +7413,7 @@
       </c>
     </row>
     <row r="167">
+      <c r="A167" t="inlineStr"/>
       <c r="B167" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -7285,9 +7444,9 @@
           <t>0.465%</t>
         </is>
       </c>
-      <c r="H167" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H167" s="1" t="inlineStr">
+        <is>
+          <t>280-226035</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -7297,6 +7456,7 @@
       </c>
     </row>
     <row r="168">
+      <c r="A168" t="inlineStr"/>
       <c r="B168" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -7327,9 +7487,9 @@
           <t>0.465%</t>
         </is>
       </c>
-      <c r="H168" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H168" s="1" t="inlineStr">
+        <is>
+          <t>280-226036</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -7339,6 +7499,7 @@
       </c>
     </row>
     <row r="169">
+      <c r="A169" t="inlineStr"/>
       <c r="B169" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -7369,9 +7530,9 @@
           <t>0.408%</t>
         </is>
       </c>
-      <c r="H169" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H169" s="1" t="inlineStr">
+        <is>
+          <t>280-226037</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -7381,6 +7542,7 @@
       </c>
     </row>
     <row r="170">
+      <c r="A170" t="inlineStr"/>
       <c r="B170" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -7411,9 +7573,9 @@
           <t>0.408%</t>
         </is>
       </c>
-      <c r="H170" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H170" s="1" t="inlineStr">
+        <is>
+          <t>280-226038</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -7423,6 +7585,7 @@
       </c>
     </row>
     <row r="171">
+      <c r="A171" t="inlineStr"/>
       <c r="B171" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -7453,9 +7616,9 @@
           <t>0.465%</t>
         </is>
       </c>
-      <c r="H171" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H171" s="1" t="inlineStr">
+        <is>
+          <t>280-226039</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -7465,6 +7628,7 @@
       </c>
     </row>
     <row r="172">
+      <c r="A172" t="inlineStr"/>
       <c r="B172" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -7495,9 +7659,9 @@
           <t>0.465%</t>
         </is>
       </c>
-      <c r="H172" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H172" s="1" t="inlineStr">
+        <is>
+          <t>280-226040</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -7507,6 +7671,7 @@
       </c>
     </row>
     <row r="173">
+      <c r="A173" t="inlineStr"/>
       <c r="B173" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -7537,9 +7702,9 @@
           <t>0.408%</t>
         </is>
       </c>
-      <c r="H173" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H173" s="1" t="inlineStr">
+        <is>
+          <t>280-226041</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -7549,6 +7714,7 @@
       </c>
     </row>
     <row r="174">
+      <c r="A174" t="inlineStr"/>
       <c r="B174" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -7579,9 +7745,9 @@
           <t>0.408%</t>
         </is>
       </c>
-      <c r="H174" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H174" s="1" t="inlineStr">
+        <is>
+          <t>280-226042</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -7591,6 +7757,7 @@
       </c>
     </row>
     <row r="175">
+      <c r="A175" t="inlineStr"/>
       <c r="B175" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -7621,9 +7788,9 @@
           <t>0.465%</t>
         </is>
       </c>
-      <c r="H175" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H175" s="1" t="inlineStr">
+        <is>
+          <t>280-226043</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -7633,6 +7800,7 @@
       </c>
     </row>
     <row r="176">
+      <c r="A176" t="inlineStr"/>
       <c r="B176" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -7663,9 +7831,9 @@
           <t>0.465%</t>
         </is>
       </c>
-      <c r="H176" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H176" s="1" t="inlineStr">
+        <is>
+          <t>280-226044</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -7675,6 +7843,7 @@
       </c>
     </row>
     <row r="177">
+      <c r="A177" t="inlineStr"/>
       <c r="B177" t="inlineStr">
         <is>
           <t>Bloque 1</t>
@@ -7705,9 +7874,9 @@
           <t>0.408%</t>
         </is>
       </c>
-      <c r="H177" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H177" s="1" t="inlineStr">
+        <is>
+          <t>280-226045</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -7717,6 +7886,7 @@
       </c>
     </row>
     <row r="178">
+      <c r="A178" t="inlineStr"/>
       <c r="B178" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -7747,9 +7917,9 @@
           <t>0.465%</t>
         </is>
       </c>
-      <c r="H178" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H178" s="1" t="inlineStr">
+        <is>
+          <t>280-226046</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -7759,6 +7929,7 @@
       </c>
     </row>
     <row r="179">
+      <c r="A179" t="inlineStr"/>
       <c r="B179" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -7789,9 +7960,9 @@
           <t>0.365%</t>
         </is>
       </c>
-      <c r="H179" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H179" s="1" t="inlineStr">
+        <is>
+          <t>280-226047</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -7801,6 +7972,7 @@
       </c>
     </row>
     <row r="180">
+      <c r="A180" t="inlineStr"/>
       <c r="B180" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -7831,9 +8003,9 @@
           <t>0.365%</t>
         </is>
       </c>
-      <c r="H180" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H180" s="1" t="inlineStr">
+        <is>
+          <t>280-226048</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -7843,6 +8015,7 @@
       </c>
     </row>
     <row r="181">
+      <c r="A181" t="inlineStr"/>
       <c r="B181" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -7873,9 +8046,9 @@
           <t>0.465%</t>
         </is>
       </c>
-      <c r="H181" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H181" s="1" t="inlineStr">
+        <is>
+          <t>280-226049</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -7885,6 +8058,7 @@
       </c>
     </row>
     <row r="182">
+      <c r="A182" t="inlineStr"/>
       <c r="B182" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -7915,9 +8089,9 @@
           <t>0.465%</t>
         </is>
       </c>
-      <c r="H182" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H182" s="1" t="inlineStr">
+        <is>
+          <t>280-226050</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -7927,6 +8101,7 @@
       </c>
     </row>
     <row r="183">
+      <c r="A183" t="inlineStr"/>
       <c r="B183" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -7957,9 +8132,9 @@
           <t>0.365%</t>
         </is>
       </c>
-      <c r="H183" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H183" s="1" t="inlineStr">
+        <is>
+          <t>280-226051</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -7969,6 +8144,7 @@
       </c>
     </row>
     <row r="184">
+      <c r="A184" t="inlineStr"/>
       <c r="B184" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -7999,9 +8175,9 @@
           <t>0.365%</t>
         </is>
       </c>
-      <c r="H184" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H184" s="1" t="inlineStr">
+        <is>
+          <t>280-226052</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -8011,6 +8187,7 @@
       </c>
     </row>
     <row r="185">
+      <c r="A185" t="inlineStr"/>
       <c r="B185" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -8041,9 +8218,9 @@
           <t>0.465%</t>
         </is>
       </c>
-      <c r="H185" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H185" s="1" t="inlineStr">
+        <is>
+          <t>280-226053</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -8053,6 +8230,7 @@
       </c>
     </row>
     <row r="186">
+      <c r="A186" t="inlineStr"/>
       <c r="B186" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -8083,9 +8261,9 @@
           <t>0.465%</t>
         </is>
       </c>
-      <c r="H186" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H186" s="1" t="inlineStr">
+        <is>
+          <t>280-226054</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -8095,6 +8273,7 @@
       </c>
     </row>
     <row r="187">
+      <c r="A187" t="inlineStr"/>
       <c r="B187" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -8125,9 +8304,9 @@
           <t>0.365%</t>
         </is>
       </c>
-      <c r="H187" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H187" s="1" t="inlineStr">
+        <is>
+          <t>280-226055</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -8137,6 +8316,7 @@
       </c>
     </row>
     <row r="188">
+      <c r="A188" t="inlineStr"/>
       <c r="B188" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -8167,9 +8347,9 @@
           <t>0.365%</t>
         </is>
       </c>
-      <c r="H188" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H188" s="1" t="inlineStr">
+        <is>
+          <t>280-226056</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -8179,6 +8359,7 @@
       </c>
     </row>
     <row r="189">
+      <c r="A189" t="inlineStr"/>
       <c r="B189" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -8209,9 +8390,9 @@
           <t>0.465%</t>
         </is>
       </c>
-      <c r="H189" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H189" s="1" t="inlineStr">
+        <is>
+          <t>280-226057</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -8221,6 +8402,7 @@
       </c>
     </row>
     <row r="190">
+      <c r="A190" t="inlineStr"/>
       <c r="B190" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -8251,9 +8433,9 @@
           <t>0.465%</t>
         </is>
       </c>
-      <c r="H190" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H190" s="1" t="inlineStr">
+        <is>
+          <t>280-226058</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -8263,6 +8445,7 @@
       </c>
     </row>
     <row r="191">
+      <c r="A191" t="inlineStr"/>
       <c r="B191" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -8293,9 +8476,9 @@
           <t>0.365%</t>
         </is>
       </c>
-      <c r="H191" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H191" s="1" t="inlineStr">
+        <is>
+          <t>280-226059</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -8305,6 +8488,7 @@
       </c>
     </row>
     <row r="192">
+      <c r="A192" t="inlineStr"/>
       <c r="B192" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -8335,9 +8519,9 @@
           <t>0.365%</t>
         </is>
       </c>
-      <c r="H192" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H192" s="1" t="inlineStr">
+        <is>
+          <t>280-226060</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -8347,6 +8531,7 @@
       </c>
     </row>
     <row r="193">
+      <c r="A193" t="inlineStr"/>
       <c r="B193" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -8377,9 +8562,9 @@
           <t>0.465%</t>
         </is>
       </c>
-      <c r="H193" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H193" s="1" t="inlineStr">
+        <is>
+          <t>280-226061</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -8389,6 +8574,7 @@
       </c>
     </row>
     <row r="194">
+      <c r="A194" t="inlineStr"/>
       <c r="B194" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -8419,9 +8605,9 @@
           <t>0.465%</t>
         </is>
       </c>
-      <c r="H194" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H194" s="1" t="inlineStr">
+        <is>
+          <t>280-226062</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -8431,6 +8617,7 @@
       </c>
     </row>
     <row r="195">
+      <c r="A195" t="inlineStr"/>
       <c r="B195" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -8461,9 +8648,9 @@
           <t>0.365%</t>
         </is>
       </c>
-      <c r="H195" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H195" s="1" t="inlineStr">
+        <is>
+          <t>280-226063</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -8473,6 +8660,7 @@
       </c>
     </row>
     <row r="196">
+      <c r="A196" t="inlineStr"/>
       <c r="B196" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -8503,9 +8691,9 @@
           <t>0.365%</t>
         </is>
       </c>
-      <c r="H196" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H196" s="1" t="inlineStr">
+        <is>
+          <t>280-226064</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -8515,6 +8703,7 @@
       </c>
     </row>
     <row r="197">
+      <c r="A197" t="inlineStr"/>
       <c r="B197" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -8545,9 +8734,9 @@
           <t>0.465%</t>
         </is>
       </c>
-      <c r="H197" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H197" s="1" t="inlineStr">
+        <is>
+          <t>280-226065</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -8557,6 +8746,7 @@
       </c>
     </row>
     <row r="198">
+      <c r="A198" t="inlineStr"/>
       <c r="B198" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -8587,9 +8777,9 @@
           <t>0.465%</t>
         </is>
       </c>
-      <c r="H198" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H198" s="1" t="inlineStr">
+        <is>
+          <t>280-226066</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -8599,6 +8789,7 @@
       </c>
     </row>
     <row r="199">
+      <c r="A199" t="inlineStr"/>
       <c r="B199" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -8629,9 +8820,9 @@
           <t>0.365%</t>
         </is>
       </c>
-      <c r="H199" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H199" s="1" t="inlineStr">
+        <is>
+          <t>280-226067</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -8641,6 +8832,7 @@
       </c>
     </row>
     <row r="200">
+      <c r="A200" t="inlineStr"/>
       <c r="B200" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -8671,9 +8863,9 @@
           <t>0.365%</t>
         </is>
       </c>
-      <c r="H200" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H200" s="1" t="inlineStr">
+        <is>
+          <t>280-226068</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -8683,6 +8875,7 @@
       </c>
     </row>
     <row r="201">
+      <c r="A201" t="inlineStr"/>
       <c r="B201" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -8713,9 +8906,9 @@
           <t>0.465%</t>
         </is>
       </c>
-      <c r="H201" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H201" s="1" t="inlineStr">
+        <is>
+          <t>280-226069</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -8725,6 +8918,7 @@
       </c>
     </row>
     <row r="202">
+      <c r="A202" t="inlineStr"/>
       <c r="B202" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -8755,9 +8949,9 @@
           <t>0.465%</t>
         </is>
       </c>
-      <c r="H202" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H202" s="1" t="inlineStr">
+        <is>
+          <t>280-226070</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -8767,6 +8961,7 @@
       </c>
     </row>
     <row r="203">
+      <c r="A203" t="inlineStr"/>
       <c r="B203" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -8797,9 +8992,9 @@
           <t>0.365%</t>
         </is>
       </c>
-      <c r="H203" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H203" s="1" t="inlineStr">
+        <is>
+          <t>280-226071</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -8809,6 +9004,7 @@
       </c>
     </row>
     <row r="204">
+      <c r="A204" t="inlineStr"/>
       <c r="B204" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -8839,9 +9035,9 @@
           <t>0.365%</t>
         </is>
       </c>
-      <c r="H204" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H204" s="1" t="inlineStr">
+        <is>
+          <t>280-226072</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -8851,6 +9047,7 @@
       </c>
     </row>
     <row r="205">
+      <c r="A205" t="inlineStr"/>
       <c r="B205" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -8881,9 +9078,9 @@
           <t>0.465%</t>
         </is>
       </c>
-      <c r="H205" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H205" s="1" t="inlineStr">
+        <is>
+          <t>280-226073</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -8893,6 +9090,7 @@
       </c>
     </row>
     <row r="206">
+      <c r="A206" t="inlineStr"/>
       <c r="B206" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -8923,9 +9121,9 @@
           <t>0.465%</t>
         </is>
       </c>
-      <c r="H206" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H206" s="1" t="inlineStr">
+        <is>
+          <t>280-226074</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -8935,6 +9133,7 @@
       </c>
     </row>
     <row r="207">
+      <c r="A207" t="inlineStr"/>
       <c r="B207" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -8965,9 +9164,9 @@
           <t>0.365%</t>
         </is>
       </c>
-      <c r="H207" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H207" s="1" t="inlineStr">
+        <is>
+          <t>280-226075</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -8977,6 +9176,7 @@
       </c>
     </row>
     <row r="208">
+      <c r="A208" t="inlineStr"/>
       <c r="B208" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -9007,9 +9207,9 @@
           <t>0.365%</t>
         </is>
       </c>
-      <c r="H208" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H208" s="1" t="inlineStr">
+        <is>
+          <t>280-226076</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -9019,6 +9219,7 @@
       </c>
     </row>
     <row r="209">
+      <c r="A209" t="inlineStr"/>
       <c r="B209" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -9049,9 +9250,9 @@
           <t>0.465%</t>
         </is>
       </c>
-      <c r="H209" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H209" s="1" t="inlineStr">
+        <is>
+          <t>280-226077</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -9061,6 +9262,7 @@
       </c>
     </row>
     <row r="210">
+      <c r="A210" t="inlineStr"/>
       <c r="B210" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -9091,9 +9293,9 @@
           <t>0.465%</t>
         </is>
       </c>
-      <c r="H210" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H210" s="1" t="inlineStr">
+        <is>
+          <t>280-226078</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -9103,6 +9305,7 @@
       </c>
     </row>
     <row r="211">
+      <c r="A211" t="inlineStr"/>
       <c r="B211" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -9133,9 +9336,9 @@
           <t>0.365%</t>
         </is>
       </c>
-      <c r="H211" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H211" s="1" t="inlineStr">
+        <is>
+          <t>280-226079</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -9145,6 +9348,7 @@
       </c>
     </row>
     <row r="212">
+      <c r="A212" t="inlineStr"/>
       <c r="B212" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -9175,9 +9379,9 @@
           <t>0.365%</t>
         </is>
       </c>
-      <c r="H212" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H212" s="1" t="inlineStr">
+        <is>
+          <t>280-226080</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -9187,6 +9391,7 @@
       </c>
     </row>
     <row r="213">
+      <c r="A213" t="inlineStr"/>
       <c r="B213" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -9217,9 +9422,9 @@
           <t>0.465%</t>
         </is>
       </c>
-      <c r="H213" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H213" s="1" t="inlineStr">
+        <is>
+          <t>280-226081</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -9229,6 +9434,7 @@
       </c>
     </row>
     <row r="214">
+      <c r="A214" t="inlineStr"/>
       <c r="B214" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -9259,9 +9465,9 @@
           <t>0.465%</t>
         </is>
       </c>
-      <c r="H214" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H214" s="1" t="inlineStr">
+        <is>
+          <t>280-226082</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -9271,6 +9477,7 @@
       </c>
     </row>
     <row r="215">
+      <c r="A215" t="inlineStr"/>
       <c r="B215" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -9301,9 +9508,9 @@
           <t>0.365%</t>
         </is>
       </c>
-      <c r="H215" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H215" s="1" t="inlineStr">
+        <is>
+          <t>280-226083</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -9313,6 +9520,7 @@
       </c>
     </row>
     <row r="216">
+      <c r="A216" t="inlineStr"/>
       <c r="B216" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -9343,9 +9551,9 @@
           <t>0.365%</t>
         </is>
       </c>
-      <c r="H216" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H216" s="1" t="inlineStr">
+        <is>
+          <t>280-226084</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -9355,6 +9563,7 @@
       </c>
     </row>
     <row r="217">
+      <c r="A217" t="inlineStr"/>
       <c r="B217" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -9385,9 +9594,9 @@
           <t>0.465%</t>
         </is>
       </c>
-      <c r="H217" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H217" s="1" t="inlineStr">
+        <is>
+          <t>280-226085</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -9397,6 +9606,7 @@
       </c>
     </row>
     <row r="218">
+      <c r="A218" t="inlineStr"/>
       <c r="B218" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -9427,9 +9637,9 @@
           <t>0.465%</t>
         </is>
       </c>
-      <c r="H218" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H218" s="1" t="inlineStr">
+        <is>
+          <t>280-226086</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -9439,6 +9649,7 @@
       </c>
     </row>
     <row r="219">
+      <c r="A219" t="inlineStr"/>
       <c r="B219" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -9469,9 +9680,9 @@
           <t>0.365%</t>
         </is>
       </c>
-      <c r="H219" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H219" s="1" t="inlineStr">
+        <is>
+          <t>280-226087</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -9481,6 +9692,7 @@
       </c>
     </row>
     <row r="220">
+      <c r="A220" t="inlineStr"/>
       <c r="B220" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -9511,9 +9723,9 @@
           <t>0.365%</t>
         </is>
       </c>
-      <c r="H220" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H220" s="1" t="inlineStr">
+        <is>
+          <t>280-226088</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -9523,6 +9735,7 @@
       </c>
     </row>
     <row r="221">
+      <c r="A221" t="inlineStr"/>
       <c r="B221" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -9553,9 +9766,9 @@
           <t>0.465%</t>
         </is>
       </c>
-      <c r="H221" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H221" s="1" t="inlineStr">
+        <is>
+          <t>280-226089</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -9565,6 +9778,7 @@
       </c>
     </row>
     <row r="222">
+      <c r="A222" t="inlineStr"/>
       <c r="B222" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -9595,9 +9809,9 @@
           <t>0.465%</t>
         </is>
       </c>
-      <c r="H222" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H222" s="1" t="inlineStr">
+        <is>
+          <t>280-226090</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -9607,6 +9821,7 @@
       </c>
     </row>
     <row r="223">
+      <c r="A223" t="inlineStr"/>
       <c r="B223" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -9637,9 +9852,9 @@
           <t>0.365%</t>
         </is>
       </c>
-      <c r="H223" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H223" s="1" t="inlineStr">
+        <is>
+          <t>280-226091</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -9649,6 +9864,7 @@
       </c>
     </row>
     <row r="224">
+      <c r="A224" t="inlineStr"/>
       <c r="B224" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -9679,9 +9895,9 @@
           <t>0.365%</t>
         </is>
       </c>
-      <c r="H224" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H224" s="1" t="inlineStr">
+        <is>
+          <t>280-226092</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -9691,6 +9907,7 @@
       </c>
     </row>
     <row r="225">
+      <c r="A225" t="inlineStr"/>
       <c r="B225" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -9721,9 +9938,9 @@
           <t>0.465%</t>
         </is>
       </c>
-      <c r="H225" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H225" s="1" t="inlineStr">
+        <is>
+          <t>280-226093</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -9733,6 +9950,7 @@
       </c>
     </row>
     <row r="226">
+      <c r="A226" t="inlineStr"/>
       <c r="B226" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -9763,9 +9981,9 @@
           <t>0.465%</t>
         </is>
       </c>
-      <c r="H226" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H226" s="1" t="inlineStr">
+        <is>
+          <t>280-226094</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -9775,6 +9993,7 @@
       </c>
     </row>
     <row r="227">
+      <c r="A227" t="inlineStr"/>
       <c r="B227" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -9805,9 +10024,9 @@
           <t>0.365%</t>
         </is>
       </c>
-      <c r="H227" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H227" s="1" t="inlineStr">
+        <is>
+          <t>280-226095</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -9817,6 +10036,7 @@
       </c>
     </row>
     <row r="228">
+      <c r="A228" t="inlineStr"/>
       <c r="B228" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -9847,9 +10067,9 @@
           <t>0.365%</t>
         </is>
       </c>
-      <c r="H228" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H228" s="1" t="inlineStr">
+        <is>
+          <t>280-226096</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -9859,6 +10079,7 @@
       </c>
     </row>
     <row r="229">
+      <c r="A229" t="inlineStr"/>
       <c r="B229" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -9889,9 +10110,9 @@
           <t>0.465%</t>
         </is>
       </c>
-      <c r="H229" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H229" s="1" t="inlineStr">
+        <is>
+          <t>280-226097</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -9901,6 +10122,7 @@
       </c>
     </row>
     <row r="230">
+      <c r="A230" t="inlineStr"/>
       <c r="B230" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -9931,9 +10153,9 @@
           <t>0.465%</t>
         </is>
       </c>
-      <c r="H230" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H230" s="1" t="inlineStr">
+        <is>
+          <t>280-226098</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -9943,6 +10165,7 @@
       </c>
     </row>
     <row r="231">
+      <c r="A231" t="inlineStr"/>
       <c r="B231" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -9973,9 +10196,9 @@
           <t>0.365%</t>
         </is>
       </c>
-      <c r="H231" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H231" s="1" t="inlineStr">
+        <is>
+          <t>280-226099</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -9985,6 +10208,7 @@
       </c>
     </row>
     <row r="232">
+      <c r="A232" t="inlineStr"/>
       <c r="B232" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -10015,9 +10239,9 @@
           <t>0.365%</t>
         </is>
       </c>
-      <c r="H232" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H232" s="1" t="inlineStr">
+        <is>
+          <t>280-226100</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -10027,6 +10251,7 @@
       </c>
     </row>
     <row r="233">
+      <c r="A233" t="inlineStr"/>
       <c r="B233" t="inlineStr">
         <is>
           <t>Bloque 2</t>
@@ -10057,9 +10282,9 @@
           <t>0.465%</t>
         </is>
       </c>
-      <c r="H233" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
+      <c r="H233" s="1" t="inlineStr">
+        <is>
+          <t>280-226101</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -10069,11 +10294,14 @@
       </c>
     </row>
     <row r="234">
+      <c r="A234" t="inlineStr"/>
       <c r="B234" t="inlineStr">
         <is>
           <t>TOTAL APARTAMENTOS (228)</t>
         </is>
       </c>
+      <c r="C234" t="inlineStr"/>
+      <c r="D234" t="inlineStr"/>
       <c r="E234" t="inlineStr">
         <is>
           <t>11,631.40</t>
@@ -10111,6 +10339,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
+      <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
           <t>BASE DE DATOS DE PARQUEADEROS Y REGISTRO DE MATRÍCULAS</t>
@@ -10118,6 +10347,7 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
           <t>Nota: Incluye parqueaderos de carros (Sótano 1 y 2) y de motos (Fases 1 y 2).</t>
@@ -10125,6 +10355,7 @@
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
           <t>Tipo</t>
@@ -10167,6 +10398,7 @@
       </c>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -10209,6 +10441,7 @@
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -10251,6 +10484,7 @@
       </c>
     </row>
     <row r="8">
+      <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -10293,6 +10527,7 @@
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -10335,6 +10570,7 @@
       </c>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -10377,6 +10613,7 @@
       </c>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -10419,6 +10656,7 @@
       </c>
     </row>
     <row r="12">
+      <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -10461,6 +10699,7 @@
       </c>
     </row>
     <row r="13">
+      <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -10503,6 +10742,7 @@
       </c>
     </row>
     <row r="14">
+      <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -10545,6 +10785,7 @@
       </c>
     </row>
     <row r="15">
+      <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -10587,6 +10828,7 @@
       </c>
     </row>
     <row r="16">
+      <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -10629,6 +10871,7 @@
       </c>
     </row>
     <row r="17">
+      <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -10671,6 +10914,7 @@
       </c>
     </row>
     <row r="18">
+      <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -10713,6 +10957,7 @@
       </c>
     </row>
     <row r="19">
+      <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -10755,6 +11000,7 @@
       </c>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -10797,6 +11043,7 @@
       </c>
     </row>
     <row r="21">
+      <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -10839,6 +11086,7 @@
       </c>
     </row>
     <row r="22">
+      <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -10881,6 +11129,7 @@
       </c>
     </row>
     <row r="23">
+      <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -10923,6 +11172,7 @@
       </c>
     </row>
     <row r="24">
+      <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -10965,6 +11215,7 @@
       </c>
     </row>
     <row r="25">
+      <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -11007,6 +11258,7 @@
       </c>
     </row>
     <row r="26">
+      <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -11049,6 +11301,7 @@
       </c>
     </row>
     <row r="27">
+      <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -11091,6 +11344,7 @@
       </c>
     </row>
     <row r="28">
+      <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -11133,6 +11387,7 @@
       </c>
     </row>
     <row r="29">
+      <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -11175,6 +11430,7 @@
       </c>
     </row>
     <row r="30">
+      <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -11217,6 +11473,7 @@
       </c>
     </row>
     <row r="31">
+      <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -11259,6 +11516,7 @@
       </c>
     </row>
     <row r="32">
+      <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -11301,6 +11559,7 @@
       </c>
     </row>
     <row r="33">
+      <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -11343,6 +11602,7 @@
       </c>
     </row>
     <row r="34">
+      <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -11385,6 +11645,7 @@
       </c>
     </row>
     <row r="35">
+      <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -11427,6 +11688,7 @@
       </c>
     </row>
     <row r="36">
+      <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -11469,6 +11731,7 @@
       </c>
     </row>
     <row r="37">
+      <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -11511,6 +11774,7 @@
       </c>
     </row>
     <row r="38">
+      <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -11553,6 +11817,7 @@
       </c>
     </row>
     <row r="39">
+      <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -11595,6 +11860,7 @@
       </c>
     </row>
     <row r="40">
+      <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -11637,6 +11903,7 @@
       </c>
     </row>
     <row r="41">
+      <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -11679,6 +11946,7 @@
       </c>
     </row>
     <row r="42">
+      <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -11721,6 +11989,7 @@
       </c>
     </row>
     <row r="43">
+      <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -11763,6 +12032,7 @@
       </c>
     </row>
     <row r="44">
+      <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -11805,6 +12075,7 @@
       </c>
     </row>
     <row r="45">
+      <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -11847,6 +12118,7 @@
       </c>
     </row>
     <row r="46">
+      <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -11889,6 +12161,7 @@
       </c>
     </row>
     <row r="47">
+      <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -11931,6 +12204,7 @@
       </c>
     </row>
     <row r="48">
+      <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -11973,6 +12247,7 @@
       </c>
     </row>
     <row r="49">
+      <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -12015,6 +12290,7 @@
       </c>
     </row>
     <row r="50">
+      <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -12057,6 +12333,7 @@
       </c>
     </row>
     <row r="51">
+      <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -12099,6 +12376,7 @@
       </c>
     </row>
     <row r="52">
+      <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -12141,6 +12419,7 @@
       </c>
     </row>
     <row r="53">
+      <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -12183,6 +12462,7 @@
       </c>
     </row>
     <row r="54">
+      <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -12225,6 +12505,7 @@
       </c>
     </row>
     <row r="55">
+      <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -12267,6 +12548,7 @@
       </c>
     </row>
     <row r="56">
+      <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -12309,6 +12591,7 @@
       </c>
     </row>
     <row r="57">
+      <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -12351,6 +12634,7 @@
       </c>
     </row>
     <row r="58">
+      <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -12393,6 +12677,7 @@
       </c>
     </row>
     <row r="59">
+      <c r="A59" t="inlineStr"/>
       <c r="B59" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -12435,6 +12720,7 @@
       </c>
     </row>
     <row r="60">
+      <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -12477,6 +12763,7 @@
       </c>
     </row>
     <row r="61">
+      <c r="A61" t="inlineStr"/>
       <c r="B61" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -12519,6 +12806,7 @@
       </c>
     </row>
     <row r="62">
+      <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -12561,6 +12849,7 @@
       </c>
     </row>
     <row r="63">
+      <c r="A63" t="inlineStr"/>
       <c r="B63" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -12603,6 +12892,7 @@
       </c>
     </row>
     <row r="64">
+      <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -12645,6 +12935,7 @@
       </c>
     </row>
     <row r="65">
+      <c r="A65" t="inlineStr"/>
       <c r="B65" t="inlineStr">
         <is>
           <t>Carro Sótano 2</t>
@@ -12687,6 +12978,7 @@
       </c>
     </row>
     <row r="66">
+      <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -12729,6 +13021,7 @@
       </c>
     </row>
     <row r="67">
+      <c r="A67" t="inlineStr"/>
       <c r="B67" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -12771,6 +13064,7 @@
       </c>
     </row>
     <row r="68">
+      <c r="A68" t="inlineStr"/>
       <c r="B68" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -12813,6 +13107,7 @@
       </c>
     </row>
     <row r="69">
+      <c r="A69" t="inlineStr"/>
       <c r="B69" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -12855,6 +13150,7 @@
       </c>
     </row>
     <row r="70">
+      <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -12897,6 +13193,7 @@
       </c>
     </row>
     <row r="71">
+      <c r="A71" t="inlineStr"/>
       <c r="B71" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -12939,6 +13236,7 @@
       </c>
     </row>
     <row r="72">
+      <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -12981,6 +13279,7 @@
       </c>
     </row>
     <row r="73">
+      <c r="A73" t="inlineStr"/>
       <c r="B73" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -13023,6 +13322,7 @@
       </c>
     </row>
     <row r="74">
+      <c r="A74" t="inlineStr"/>
       <c r="B74" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -13065,6 +13365,7 @@
       </c>
     </row>
     <row r="75">
+      <c r="A75" t="inlineStr"/>
       <c r="B75" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -13107,6 +13408,7 @@
       </c>
     </row>
     <row r="76">
+      <c r="A76" t="inlineStr"/>
       <c r="B76" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -13149,6 +13451,7 @@
       </c>
     </row>
     <row r="77">
+      <c r="A77" t="inlineStr"/>
       <c r="B77" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -13191,6 +13494,7 @@
       </c>
     </row>
     <row r="78">
+      <c r="A78" t="inlineStr"/>
       <c r="B78" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -13233,6 +13537,7 @@
       </c>
     </row>
     <row r="79">
+      <c r="A79" t="inlineStr"/>
       <c r="B79" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -13275,6 +13580,7 @@
       </c>
     </row>
     <row r="80">
+      <c r="A80" t="inlineStr"/>
       <c r="B80" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -13317,6 +13623,7 @@
       </c>
     </row>
     <row r="81">
+      <c r="A81" t="inlineStr"/>
       <c r="B81" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -13359,6 +13666,7 @@
       </c>
     </row>
     <row r="82">
+      <c r="A82" t="inlineStr"/>
       <c r="B82" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -13401,6 +13709,7 @@
       </c>
     </row>
     <row r="83">
+      <c r="A83" t="inlineStr"/>
       <c r="B83" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -13443,6 +13752,7 @@
       </c>
     </row>
     <row r="84">
+      <c r="A84" t="inlineStr"/>
       <c r="B84" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -13485,6 +13795,7 @@
       </c>
     </row>
     <row r="85">
+      <c r="A85" t="inlineStr"/>
       <c r="B85" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -13527,6 +13838,7 @@
       </c>
     </row>
     <row r="86">
+      <c r="A86" t="inlineStr"/>
       <c r="B86" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -13569,6 +13881,7 @@
       </c>
     </row>
     <row r="87">
+      <c r="A87" t="inlineStr"/>
       <c r="B87" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -13611,6 +13924,7 @@
       </c>
     </row>
     <row r="88">
+      <c r="A88" t="inlineStr"/>
       <c r="B88" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -13653,6 +13967,7 @@
       </c>
     </row>
     <row r="89">
+      <c r="A89" t="inlineStr"/>
       <c r="B89" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -13695,6 +14010,7 @@
       </c>
     </row>
     <row r="90">
+      <c r="A90" t="inlineStr"/>
       <c r="B90" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -13737,6 +14053,7 @@
       </c>
     </row>
     <row r="91">
+      <c r="A91" t="inlineStr"/>
       <c r="B91" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -13779,6 +14096,7 @@
       </c>
     </row>
     <row r="92">
+      <c r="A92" t="inlineStr"/>
       <c r="B92" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -13821,6 +14139,7 @@
       </c>
     </row>
     <row r="93">
+      <c r="A93" t="inlineStr"/>
       <c r="B93" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -13863,6 +14182,7 @@
       </c>
     </row>
     <row r="94">
+      <c r="A94" t="inlineStr"/>
       <c r="B94" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -13905,6 +14225,7 @@
       </c>
     </row>
     <row r="95">
+      <c r="A95" t="inlineStr"/>
       <c r="B95" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -13947,6 +14268,7 @@
       </c>
     </row>
     <row r="96">
+      <c r="A96" t="inlineStr"/>
       <c r="B96" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -13989,6 +14311,7 @@
       </c>
     </row>
     <row r="97">
+      <c r="A97" t="inlineStr"/>
       <c r="B97" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -14031,6 +14354,7 @@
       </c>
     </row>
     <row r="98">
+      <c r="A98" t="inlineStr"/>
       <c r="B98" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -14073,6 +14397,7 @@
       </c>
     </row>
     <row r="99">
+      <c r="A99" t="inlineStr"/>
       <c r="B99" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -14115,6 +14440,7 @@
       </c>
     </row>
     <row r="100">
+      <c r="A100" t="inlineStr"/>
       <c r="B100" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -14157,6 +14483,7 @@
       </c>
     </row>
     <row r="101">
+      <c r="A101" t="inlineStr"/>
       <c r="B101" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -14199,6 +14526,7 @@
       </c>
     </row>
     <row r="102">
+      <c r="A102" t="inlineStr"/>
       <c r="B102" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -14241,6 +14569,7 @@
       </c>
     </row>
     <row r="103">
+      <c r="A103" t="inlineStr"/>
       <c r="B103" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -14283,6 +14612,7 @@
       </c>
     </row>
     <row r="104">
+      <c r="A104" t="inlineStr"/>
       <c r="B104" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -14325,6 +14655,7 @@
       </c>
     </row>
     <row r="105">
+      <c r="A105" t="inlineStr"/>
       <c r="B105" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -14367,6 +14698,7 @@
       </c>
     </row>
     <row r="106">
+      <c r="A106" t="inlineStr"/>
       <c r="B106" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -14409,6 +14741,7 @@
       </c>
     </row>
     <row r="107">
+      <c r="A107" t="inlineStr"/>
       <c r="B107" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -14451,6 +14784,7 @@
       </c>
     </row>
     <row r="108">
+      <c r="A108" t="inlineStr"/>
       <c r="B108" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -14493,6 +14827,7 @@
       </c>
     </row>
     <row r="109">
+      <c r="A109" t="inlineStr"/>
       <c r="B109" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -14535,6 +14870,7 @@
       </c>
     </row>
     <row r="110">
+      <c r="A110" t="inlineStr"/>
       <c r="B110" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -14577,6 +14913,7 @@
       </c>
     </row>
     <row r="111">
+      <c r="A111" t="inlineStr"/>
       <c r="B111" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -14619,6 +14956,7 @@
       </c>
     </row>
     <row r="112">
+      <c r="A112" t="inlineStr"/>
       <c r="B112" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -14661,6 +14999,7 @@
       </c>
     </row>
     <row r="113">
+      <c r="A113" t="inlineStr"/>
       <c r="B113" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -14703,6 +15042,7 @@
       </c>
     </row>
     <row r="114">
+      <c r="A114" t="inlineStr"/>
       <c r="B114" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -14745,6 +15085,7 @@
       </c>
     </row>
     <row r="115">
+      <c r="A115" t="inlineStr"/>
       <c r="B115" t="inlineStr">
         <is>
           <t>Carro Sótano 1</t>
@@ -14787,6 +15128,7 @@
       </c>
     </row>
     <row r="116">
+      <c r="A116" t="inlineStr"/>
       <c r="B116" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -14829,6 +15171,7 @@
       </c>
     </row>
     <row r="117">
+      <c r="A117" t="inlineStr"/>
       <c r="B117" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -14871,6 +15214,7 @@
       </c>
     </row>
     <row r="118">
+      <c r="A118" t="inlineStr"/>
       <c r="B118" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -14913,6 +15257,7 @@
       </c>
     </row>
     <row r="119">
+      <c r="A119" t="inlineStr"/>
       <c r="B119" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -14955,6 +15300,7 @@
       </c>
     </row>
     <row r="120">
+      <c r="A120" t="inlineStr"/>
       <c r="B120" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -14997,6 +15343,7 @@
       </c>
     </row>
     <row r="121">
+      <c r="A121" t="inlineStr"/>
       <c r="B121" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -15039,6 +15386,7 @@
       </c>
     </row>
     <row r="122">
+      <c r="A122" t="inlineStr"/>
       <c r="B122" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -15081,6 +15429,7 @@
       </c>
     </row>
     <row r="123">
+      <c r="A123" t="inlineStr"/>
       <c r="B123" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -15123,6 +15472,7 @@
       </c>
     </row>
     <row r="124">
+      <c r="A124" t="inlineStr"/>
       <c r="B124" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -15165,6 +15515,7 @@
       </c>
     </row>
     <row r="125">
+      <c r="A125" t="inlineStr"/>
       <c r="B125" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -15207,6 +15558,7 @@
       </c>
     </row>
     <row r="126">
+      <c r="A126" t="inlineStr"/>
       <c r="B126" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -15249,6 +15601,7 @@
       </c>
     </row>
     <row r="127">
+      <c r="A127" t="inlineStr"/>
       <c r="B127" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -15291,6 +15644,7 @@
       </c>
     </row>
     <row r="128">
+      <c r="A128" t="inlineStr"/>
       <c r="B128" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -15333,6 +15687,7 @@
       </c>
     </row>
     <row r="129">
+      <c r="A129" t="inlineStr"/>
       <c r="B129" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -15375,6 +15730,7 @@
       </c>
     </row>
     <row r="130">
+      <c r="A130" t="inlineStr"/>
       <c r="B130" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -15417,6 +15773,7 @@
       </c>
     </row>
     <row r="131">
+      <c r="A131" t="inlineStr"/>
       <c r="B131" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -15459,6 +15816,7 @@
       </c>
     </row>
     <row r="132">
+      <c r="A132" t="inlineStr"/>
       <c r="B132" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -15501,6 +15859,7 @@
       </c>
     </row>
     <row r="133">
+      <c r="A133" t="inlineStr"/>
       <c r="B133" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -15543,6 +15902,7 @@
       </c>
     </row>
     <row r="134">
+      <c r="A134" t="inlineStr"/>
       <c r="B134" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -15585,6 +15945,7 @@
       </c>
     </row>
     <row r="135">
+      <c r="A135" t="inlineStr"/>
       <c r="B135" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -15627,6 +15988,7 @@
       </c>
     </row>
     <row r="136">
+      <c r="A136" t="inlineStr"/>
       <c r="B136" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -15669,6 +16031,7 @@
       </c>
     </row>
     <row r="137">
+      <c r="A137" t="inlineStr"/>
       <c r="B137" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -15711,6 +16074,7 @@
       </c>
     </row>
     <row r="138">
+      <c r="A138" t="inlineStr"/>
       <c r="B138" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -15753,6 +16117,7 @@
       </c>
     </row>
     <row r="139">
+      <c r="A139" t="inlineStr"/>
       <c r="B139" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -15795,6 +16160,7 @@
       </c>
     </row>
     <row r="140">
+      <c r="A140" t="inlineStr"/>
       <c r="B140" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -15837,6 +16203,7 @@
       </c>
     </row>
     <row r="141">
+      <c r="A141" t="inlineStr"/>
       <c r="B141" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -15879,6 +16246,7 @@
       </c>
     </row>
     <row r="142">
+      <c r="A142" t="inlineStr"/>
       <c r="B142" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -15921,6 +16289,7 @@
       </c>
     </row>
     <row r="143">
+      <c r="A143" t="inlineStr"/>
       <c r="B143" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -15963,6 +16332,7 @@
       </c>
     </row>
     <row r="144">
+      <c r="A144" t="inlineStr"/>
       <c r="B144" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -16005,6 +16375,7 @@
       </c>
     </row>
     <row r="145">
+      <c r="A145" t="inlineStr"/>
       <c r="B145" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -16047,6 +16418,7 @@
       </c>
     </row>
     <row r="146">
+      <c r="A146" t="inlineStr"/>
       <c r="B146" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -16089,6 +16461,7 @@
       </c>
     </row>
     <row r="147">
+      <c r="A147" t="inlineStr"/>
       <c r="B147" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -16131,6 +16504,7 @@
       </c>
     </row>
     <row r="148">
+      <c r="A148" t="inlineStr"/>
       <c r="B148" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -16173,6 +16547,7 @@
       </c>
     </row>
     <row r="149">
+      <c r="A149" t="inlineStr"/>
       <c r="B149" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -16215,6 +16590,7 @@
       </c>
     </row>
     <row r="150">
+      <c r="A150" t="inlineStr"/>
       <c r="B150" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -16257,6 +16633,7 @@
       </c>
     </row>
     <row r="151">
+      <c r="A151" t="inlineStr"/>
       <c r="B151" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -16299,6 +16676,7 @@
       </c>
     </row>
     <row r="152">
+      <c r="A152" t="inlineStr"/>
       <c r="B152" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -16341,6 +16719,7 @@
       </c>
     </row>
     <row r="153">
+      <c r="A153" t="inlineStr"/>
       <c r="B153" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -16383,6 +16762,7 @@
       </c>
     </row>
     <row r="154">
+      <c r="A154" t="inlineStr"/>
       <c r="B154" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -16425,6 +16805,7 @@
       </c>
     </row>
     <row r="155">
+      <c r="A155" t="inlineStr"/>
       <c r="B155" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -16467,6 +16848,7 @@
       </c>
     </row>
     <row r="156">
+      <c r="A156" t="inlineStr"/>
       <c r="B156" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -16509,6 +16891,7 @@
       </c>
     </row>
     <row r="157">
+      <c r="A157" t="inlineStr"/>
       <c r="B157" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -16551,6 +16934,7 @@
       </c>
     </row>
     <row r="158">
+      <c r="A158" t="inlineStr"/>
       <c r="B158" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -16593,6 +16977,7 @@
       </c>
     </row>
     <row r="159">
+      <c r="A159" t="inlineStr"/>
       <c r="B159" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -16635,6 +17020,7 @@
       </c>
     </row>
     <row r="160">
+      <c r="A160" t="inlineStr"/>
       <c r="B160" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -16677,6 +17063,7 @@
       </c>
     </row>
     <row r="161">
+      <c r="A161" t="inlineStr"/>
       <c r="B161" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -16719,6 +17106,7 @@
       </c>
     </row>
     <row r="162">
+      <c r="A162" t="inlineStr"/>
       <c r="B162" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -16761,6 +17149,7 @@
       </c>
     </row>
     <row r="163">
+      <c r="A163" t="inlineStr"/>
       <c r="B163" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -16803,6 +17192,7 @@
       </c>
     </row>
     <row r="164">
+      <c r="A164" t="inlineStr"/>
       <c r="B164" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -16845,6 +17235,7 @@
       </c>
     </row>
     <row r="165">
+      <c r="A165" t="inlineStr"/>
       <c r="B165" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -16887,6 +17278,7 @@
       </c>
     </row>
     <row r="166">
+      <c r="A166" t="inlineStr"/>
       <c r="B166" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -16929,6 +17321,7 @@
       </c>
     </row>
     <row r="167">
+      <c r="A167" t="inlineStr"/>
       <c r="B167" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -16971,6 +17364,7 @@
       </c>
     </row>
     <row r="168">
+      <c r="A168" t="inlineStr"/>
       <c r="B168" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -17013,6 +17407,7 @@
       </c>
     </row>
     <row r="169">
+      <c r="A169" t="inlineStr"/>
       <c r="B169" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -17055,6 +17450,7 @@
       </c>
     </row>
     <row r="170">
+      <c r="A170" t="inlineStr"/>
       <c r="B170" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -17097,6 +17493,7 @@
       </c>
     </row>
     <row r="171">
+      <c r="A171" t="inlineStr"/>
       <c r="B171" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -17139,6 +17536,7 @@
       </c>
     </row>
     <row r="172">
+      <c r="A172" t="inlineStr"/>
       <c r="B172" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -17181,6 +17579,7 @@
       </c>
     </row>
     <row r="173">
+      <c r="A173" t="inlineStr"/>
       <c r="B173" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -17223,6 +17622,7 @@
       </c>
     </row>
     <row r="174">
+      <c r="A174" t="inlineStr"/>
       <c r="B174" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -17265,6 +17665,7 @@
       </c>
     </row>
     <row r="175">
+      <c r="A175" t="inlineStr"/>
       <c r="B175" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -17307,6 +17708,7 @@
       </c>
     </row>
     <row r="176">
+      <c r="A176" t="inlineStr"/>
       <c r="B176" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -17349,6 +17751,7 @@
       </c>
     </row>
     <row r="177">
+      <c r="A177" t="inlineStr"/>
       <c r="B177" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -17391,6 +17794,7 @@
       </c>
     </row>
     <row r="178">
+      <c r="A178" t="inlineStr"/>
       <c r="B178" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -17433,6 +17837,7 @@
       </c>
     </row>
     <row r="179">
+      <c r="A179" t="inlineStr"/>
       <c r="B179" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -17475,6 +17880,7 @@
       </c>
     </row>
     <row r="180">
+      <c r="A180" t="inlineStr"/>
       <c r="B180" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -17517,6 +17923,7 @@
       </c>
     </row>
     <row r="181">
+      <c r="A181" t="inlineStr"/>
       <c r="B181" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -17559,6 +17966,7 @@
       </c>
     </row>
     <row r="182">
+      <c r="A182" t="inlineStr"/>
       <c r="B182" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -17601,6 +18009,7 @@
       </c>
     </row>
     <row r="183">
+      <c r="A183" t="inlineStr"/>
       <c r="B183" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -17643,6 +18052,7 @@
       </c>
     </row>
     <row r="184">
+      <c r="A184" t="inlineStr"/>
       <c r="B184" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -17685,6 +18095,7 @@
       </c>
     </row>
     <row r="185">
+      <c r="A185" t="inlineStr"/>
       <c r="B185" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -17727,6 +18138,7 @@
       </c>
     </row>
     <row r="186">
+      <c r="A186" t="inlineStr"/>
       <c r="B186" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -17769,6 +18181,7 @@
       </c>
     </row>
     <row r="187">
+      <c r="A187" t="inlineStr"/>
       <c r="B187" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -17811,6 +18224,7 @@
       </c>
     </row>
     <row r="188">
+      <c r="A188" t="inlineStr"/>
       <c r="B188" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -17853,6 +18267,7 @@
       </c>
     </row>
     <row r="189">
+      <c r="A189" t="inlineStr"/>
       <c r="B189" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -17895,6 +18310,7 @@
       </c>
     </row>
     <row r="190">
+      <c r="A190" t="inlineStr"/>
       <c r="B190" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -17937,6 +18353,7 @@
       </c>
     </row>
     <row r="191">
+      <c r="A191" t="inlineStr"/>
       <c r="B191" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -17979,6 +18396,7 @@
       </c>
     </row>
     <row r="192">
+      <c r="A192" t="inlineStr"/>
       <c r="B192" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -18021,6 +18439,7 @@
       </c>
     </row>
     <row r="193">
+      <c r="A193" t="inlineStr"/>
       <c r="B193" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -18063,6 +18482,7 @@
       </c>
     </row>
     <row r="194">
+      <c r="A194" t="inlineStr"/>
       <c r="B194" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -18105,6 +18525,7 @@
       </c>
     </row>
     <row r="195">
+      <c r="A195" t="inlineStr"/>
       <c r="B195" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -18147,6 +18568,7 @@
       </c>
     </row>
     <row r="196">
+      <c r="A196" t="inlineStr"/>
       <c r="B196" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -18189,6 +18611,7 @@
       </c>
     </row>
     <row r="197">
+      <c r="A197" t="inlineStr"/>
       <c r="B197" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -18231,6 +18654,7 @@
       </c>
     </row>
     <row r="198">
+      <c r="A198" t="inlineStr"/>
       <c r="B198" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -18273,6 +18697,7 @@
       </c>
     </row>
     <row r="199">
+      <c r="A199" t="inlineStr"/>
       <c r="B199" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -18315,6 +18740,7 @@
       </c>
     </row>
     <row r="200">
+      <c r="A200" t="inlineStr"/>
       <c r="B200" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -18357,6 +18783,7 @@
       </c>
     </row>
     <row r="201">
+      <c r="A201" t="inlineStr"/>
       <c r="B201" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -18399,6 +18826,7 @@
       </c>
     </row>
     <row r="202">
+      <c r="A202" t="inlineStr"/>
       <c r="B202" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -18441,6 +18869,7 @@
       </c>
     </row>
     <row r="203">
+      <c r="A203" t="inlineStr"/>
       <c r="B203" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -18483,6 +18912,7 @@
       </c>
     </row>
     <row r="204">
+      <c r="A204" t="inlineStr"/>
       <c r="B204" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -18525,6 +18955,7 @@
       </c>
     </row>
     <row r="205">
+      <c r="A205" t="inlineStr"/>
       <c r="B205" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -18567,6 +18998,7 @@
       </c>
     </row>
     <row r="206">
+      <c r="A206" t="inlineStr"/>
       <c r="B206" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -18609,6 +19041,7 @@
       </c>
     </row>
     <row r="207">
+      <c r="A207" t="inlineStr"/>
       <c r="B207" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa I)</t>
@@ -18651,6 +19084,7 @@
       </c>
     </row>
     <row r="208">
+      <c r="A208" t="inlineStr"/>
       <c r="B208" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa II)</t>
@@ -18693,6 +19127,7 @@
       </c>
     </row>
     <row r="209">
+      <c r="A209" t="inlineStr"/>
       <c r="B209" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa II)</t>
@@ -18735,6 +19170,7 @@
       </c>
     </row>
     <row r="210">
+      <c r="A210" t="inlineStr"/>
       <c r="B210" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa II)</t>
@@ -18777,6 +19213,7 @@
       </c>
     </row>
     <row r="211">
+      <c r="A211" t="inlineStr"/>
       <c r="B211" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa II)</t>
@@ -18819,6 +19256,7 @@
       </c>
     </row>
     <row r="212">
+      <c r="A212" t="inlineStr"/>
       <c r="B212" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa II)</t>
@@ -18861,6 +19299,7 @@
       </c>
     </row>
     <row r="213">
+      <c r="A213" t="inlineStr"/>
       <c r="B213" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa II)</t>
@@ -18903,6 +19342,7 @@
       </c>
     </row>
     <row r="214">
+      <c r="A214" t="inlineStr"/>
       <c r="B214" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa II)</t>
@@ -18945,6 +19385,7 @@
       </c>
     </row>
     <row r="215">
+      <c r="A215" t="inlineStr"/>
       <c r="B215" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa II)</t>
@@ -18987,6 +19428,7 @@
       </c>
     </row>
     <row r="216">
+      <c r="A216" t="inlineStr"/>
       <c r="B216" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa II)</t>
@@ -19029,6 +19471,7 @@
       </c>
     </row>
     <row r="217">
+      <c r="A217" t="inlineStr"/>
       <c r="B217" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa II)</t>
@@ -19071,6 +19514,7 @@
       </c>
     </row>
     <row r="218">
+      <c r="A218" t="inlineStr"/>
       <c r="B218" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa II)</t>
@@ -19113,6 +19557,7 @@
       </c>
     </row>
     <row r="219">
+      <c r="A219" t="inlineStr"/>
       <c r="B219" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa II)</t>
@@ -19155,6 +19600,7 @@
       </c>
     </row>
     <row r="220">
+      <c r="A220" t="inlineStr"/>
       <c r="B220" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa II)</t>
@@ -19197,6 +19643,7 @@
       </c>
     </row>
     <row r="221">
+      <c r="A221" t="inlineStr"/>
       <c r="B221" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa II)</t>
@@ -19239,6 +19686,7 @@
       </c>
     </row>
     <row r="222">
+      <c r="A222" t="inlineStr"/>
       <c r="B222" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa II)</t>
@@ -19281,6 +19729,7 @@
       </c>
     </row>
     <row r="223">
+      <c r="A223" t="inlineStr"/>
       <c r="B223" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa II)</t>
@@ -19311,18 +19760,19 @@
           <t>0.013%</t>
         </is>
       </c>
-      <c r="H223" s="3" t="inlineStr">
+      <c r="H223" s="2" t="inlineStr">
         <is>
           <t>280-21XXXX</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>AMBIGUA: revisar 280-226117, 280-226125</t>
+          <t>AMBIGUA: revisar manualmente opciones 280-226117, 280-226125</t>
         </is>
       </c>
     </row>
     <row r="224">
+      <c r="A224" t="inlineStr"/>
       <c r="B224" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa II)</t>
@@ -19365,6 +19815,7 @@
       </c>
     </row>
     <row r="225">
+      <c r="A225" t="inlineStr"/>
       <c r="B225" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa II)</t>
@@ -19407,6 +19858,7 @@
       </c>
     </row>
     <row r="226">
+      <c r="A226" t="inlineStr"/>
       <c r="B226" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa II)</t>
@@ -19449,6 +19901,7 @@
       </c>
     </row>
     <row r="227">
+      <c r="A227" t="inlineStr"/>
       <c r="B227" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa II)</t>
@@ -19491,6 +19944,7 @@
       </c>
     </row>
     <row r="228">
+      <c r="A228" t="inlineStr"/>
       <c r="B228" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa II)</t>
@@ -19521,485 +19975,499 @@
           <t>0.013%</t>
         </is>
       </c>
-      <c r="H228" s="2" t="inlineStr">
+      <c r="H228" s="1" t="inlineStr">
+        <is>
+          <t>280-226122</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>PENDIENTE: administración no tiene matrícula; residente debe digitar manualmente</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr"/>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Moto Privada (Etapa II)</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Moto 66</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Patio de Motos (Segunda Etapa)</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>0.024%</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>0.013%</t>
+        </is>
+      </c>
+      <c r="H229" s="1" t="inlineStr">
+        <is>
+          <t>280-226123</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>PENDIENTE: administración no tiene matrícula; residente debe digitar manualmente</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr"/>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Moto Privada (Etapa II)</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Moto 67</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Patio de Motos (Segunda Etapa)</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>0.024%</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>0.013%</t>
+        </is>
+      </c>
+      <c r="H230" s="1" t="inlineStr">
+        <is>
+          <t>280-226124</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>Completada desde bienes santa sofia (2).xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr"/>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Moto Privada (Etapa II)</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Moto 68</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Patio de Motos (Segunda Etapa)</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>0.024%</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>0.013%</t>
+        </is>
+      </c>
+      <c r="H231" s="2" t="inlineStr">
         <is>
           <t>280-21XXXX</t>
         </is>
       </c>
-      <c r="I228" t="inlineStr">
+      <c r="I231" t="inlineStr">
         <is>
           <t>PENDIENTE: administración no tiene matrícula; residente debe digitar manualmente</t>
         </is>
       </c>
     </row>
-    <row r="229">
-      <c r="B229" t="inlineStr">
+    <row r="232">
+      <c r="A232" t="inlineStr"/>
+      <c r="B232" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa II)</t>
         </is>
       </c>
-      <c r="C229" t="inlineStr">
-        <is>
-          <t>Moto 66</t>
-        </is>
-      </c>
-      <c r="D229" t="inlineStr">
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Moto 69</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
         <is>
           <t>Patio de Motos (Segunda Etapa)</t>
         </is>
       </c>
-      <c r="E229" t="inlineStr">
+      <c r="E232" t="inlineStr">
         <is>
           <t>1.60</t>
         </is>
       </c>
-      <c r="F229" t="inlineStr">
+      <c r="F232" t="inlineStr">
         <is>
           <t>0.024%</t>
         </is>
       </c>
-      <c r="G229" t="inlineStr">
+      <c r="G232" t="inlineStr">
         <is>
           <t>0.013%</t>
         </is>
       </c>
-      <c r="H229" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
-        </is>
-      </c>
-      <c r="I229" t="inlineStr">
+      <c r="H232" s="1" t="inlineStr">
+        <is>
+          <t>280-226126</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
         <is>
           <t>PENDIENTE: administración no tiene matrícula; residente debe digitar manualmente</t>
         </is>
       </c>
     </row>
-    <row r="230">
-      <c r="B230" t="inlineStr">
+    <row r="233">
+      <c r="A233" t="inlineStr"/>
+      <c r="B233" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa II)</t>
         </is>
       </c>
-      <c r="C230" t="inlineStr">
-        <is>
-          <t>Moto 67</t>
-        </is>
-      </c>
-      <c r="D230" t="inlineStr">
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Moto 70</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
         <is>
           <t>Patio de Motos (Segunda Etapa)</t>
         </is>
       </c>
-      <c r="E230" t="inlineStr">
+      <c r="E233" t="inlineStr">
         <is>
           <t>1.60</t>
         </is>
       </c>
-      <c r="F230" t="inlineStr">
+      <c r="F233" t="inlineStr">
         <is>
           <t>0.024%</t>
         </is>
       </c>
-      <c r="G230" t="inlineStr">
+      <c r="G233" t="inlineStr">
         <is>
           <t>0.013%</t>
         </is>
       </c>
-      <c r="H230" s="1" t="inlineStr">
-        <is>
-          <t>280-226124</t>
-        </is>
-      </c>
-      <c r="I230" t="inlineStr">
+      <c r="H233" s="1" t="inlineStr">
+        <is>
+          <t>280-226127</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
         <is>
           <t>Completada desde bienes santa sofia (2).xlsx</t>
         </is>
       </c>
     </row>
-    <row r="231">
-      <c r="B231" t="inlineStr">
+    <row r="234">
+      <c r="A234" t="inlineStr"/>
+      <c r="B234" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa II)</t>
         </is>
       </c>
-      <c r="C231" t="inlineStr">
-        <is>
-          <t>Moto 68</t>
-        </is>
-      </c>
-      <c r="D231" t="inlineStr">
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Moto 71</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
         <is>
           <t>Patio de Motos (Segunda Etapa)</t>
         </is>
       </c>
-      <c r="E231" t="inlineStr">
+      <c r="E234" t="inlineStr">
         <is>
           <t>1.60</t>
         </is>
       </c>
-      <c r="F231" t="inlineStr">
+      <c r="F234" t="inlineStr">
         <is>
           <t>0.024%</t>
         </is>
       </c>
-      <c r="G231" t="inlineStr">
+      <c r="G234" t="inlineStr">
         <is>
           <t>0.013%</t>
         </is>
       </c>
-      <c r="H231" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
-        </is>
-      </c>
-      <c r="I231" t="inlineStr">
-        <is>
-          <t>PENDIENTE: administración no tiene matrícula; residente debe digitar manualmente</t>
-        </is>
-      </c>
-    </row>
-    <row r="232">
-      <c r="B232" t="inlineStr">
+      <c r="H234" s="1" t="inlineStr">
+        <is>
+          <t>280-226128</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>Completada desde bienes santa sofia (2).xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr"/>
+      <c r="B235" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa II)</t>
         </is>
       </c>
-      <c r="C232" t="inlineStr">
-        <is>
-          <t>Moto 69</t>
-        </is>
-      </c>
-      <c r="D232" t="inlineStr">
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Moto 72</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
         <is>
           <t>Patio de Motos (Segunda Etapa)</t>
         </is>
       </c>
-      <c r="E232" t="inlineStr">
+      <c r="E235" t="inlineStr">
         <is>
           <t>1.60</t>
         </is>
       </c>
-      <c r="F232" t="inlineStr">
+      <c r="F235" t="inlineStr">
         <is>
           <t>0.024%</t>
         </is>
       </c>
-      <c r="G232" t="inlineStr">
+      <c r="G235" t="inlineStr">
         <is>
           <t>0.013%</t>
         </is>
       </c>
-      <c r="H232" s="2" t="inlineStr">
-        <is>
-          <t>280-21XXXX</t>
-        </is>
-      </c>
-      <c r="I232" t="inlineStr">
-        <is>
-          <t>PENDIENTE: administración no tiene matrícula; residente debe digitar manualmente</t>
-        </is>
-      </c>
-    </row>
-    <row r="233">
-      <c r="B233" t="inlineStr">
+      <c r="H235" s="1" t="inlineStr">
+        <is>
+          <t>280-226129</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>Completada desde bienes santa sofia (2).xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr"/>
+      <c r="B236" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa II)</t>
         </is>
       </c>
-      <c r="C233" t="inlineStr">
-        <is>
-          <t>Moto 70</t>
-        </is>
-      </c>
-      <c r="D233" t="inlineStr">
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Moto 73</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
         <is>
           <t>Patio de Motos (Segunda Etapa)</t>
         </is>
       </c>
-      <c r="E233" t="inlineStr">
+      <c r="E236" t="inlineStr">
         <is>
           <t>1.60</t>
         </is>
       </c>
-      <c r="F233" t="inlineStr">
+      <c r="F236" t="inlineStr">
         <is>
           <t>0.024%</t>
         </is>
       </c>
-      <c r="G233" t="inlineStr">
+      <c r="G236" t="inlineStr">
         <is>
           <t>0.013%</t>
         </is>
       </c>
-      <c r="H233" s="1" t="inlineStr">
-        <is>
-          <t>280-226127</t>
-        </is>
-      </c>
-      <c r="I233" t="inlineStr">
+      <c r="H236" s="1" t="inlineStr">
+        <is>
+          <t>280-226130</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
         <is>
           <t>Completada desde bienes santa sofia (2).xlsx</t>
         </is>
       </c>
     </row>
-    <row r="234">
-      <c r="B234" t="inlineStr">
+    <row r="237">
+      <c r="A237" t="inlineStr"/>
+      <c r="B237" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa II)</t>
         </is>
       </c>
-      <c r="C234" t="inlineStr">
-        <is>
-          <t>Moto 71</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr">
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Moto 74</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
         <is>
           <t>Patio de Motos (Segunda Etapa)</t>
         </is>
       </c>
-      <c r="E234" t="inlineStr">
+      <c r="E237" t="inlineStr">
         <is>
           <t>1.60</t>
         </is>
       </c>
-      <c r="F234" t="inlineStr">
+      <c r="F237" t="inlineStr">
         <is>
           <t>0.024%</t>
         </is>
       </c>
-      <c r="G234" t="inlineStr">
+      <c r="G237" t="inlineStr">
         <is>
           <t>0.013%</t>
         </is>
       </c>
-      <c r="H234" s="1" t="inlineStr">
-        <is>
-          <t>280-226128</t>
-        </is>
-      </c>
-      <c r="I234" t="inlineStr">
+      <c r="H237" s="1" t="inlineStr">
+        <is>
+          <t>280-226131</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
         <is>
           <t>Completada desde bienes santa sofia (2).xlsx</t>
         </is>
       </c>
     </row>
-    <row r="235">
-      <c r="B235" t="inlineStr">
+    <row r="238">
+      <c r="A238" t="inlineStr"/>
+      <c r="B238" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa II)</t>
         </is>
       </c>
-      <c r="C235" t="inlineStr">
-        <is>
-          <t>Moto 72</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr">
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Moto 75</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
         <is>
           <t>Patio de Motos (Segunda Etapa)</t>
         </is>
       </c>
-      <c r="E235" t="inlineStr">
+      <c r="E238" t="inlineStr">
         <is>
           <t>1.60</t>
         </is>
       </c>
-      <c r="F235" t="inlineStr">
+      <c r="F238" t="inlineStr">
         <is>
           <t>0.024%</t>
         </is>
       </c>
-      <c r="G235" t="inlineStr">
+      <c r="G238" t="inlineStr">
         <is>
           <t>0.013%</t>
         </is>
       </c>
-      <c r="H235" s="1" t="inlineStr">
-        <is>
-          <t>280-226129</t>
-        </is>
-      </c>
-      <c r="I235" t="inlineStr">
+      <c r="H238" s="1" t="inlineStr">
+        <is>
+          <t>280-226132</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
         <is>
           <t>Completada desde bienes santa sofia (2).xlsx</t>
         </is>
       </c>
     </row>
-    <row r="236">
-      <c r="B236" t="inlineStr">
+    <row r="239">
+      <c r="A239" t="inlineStr"/>
+      <c r="B239" t="inlineStr">
         <is>
           <t>Moto Privada (Etapa II)</t>
         </is>
       </c>
-      <c r="C236" t="inlineStr">
-        <is>
-          <t>Moto 73</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr">
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Moto 76</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
         <is>
           <t>Patio de Motos (Segunda Etapa)</t>
         </is>
       </c>
-      <c r="E236" t="inlineStr">
+      <c r="E239" t="inlineStr">
         <is>
           <t>1.60</t>
         </is>
       </c>
-      <c r="F236" t="inlineStr">
+      <c r="F239" t="inlineStr">
         <is>
           <t>0.024%</t>
         </is>
       </c>
-      <c r="G236" t="inlineStr">
+      <c r="G239" t="inlineStr">
         <is>
           <t>0.013%</t>
         </is>
       </c>
-      <c r="H236" s="1" t="inlineStr">
-        <is>
-          <t>280-226130</t>
-        </is>
-      </c>
-      <c r="I236" t="inlineStr">
+      <c r="H239" s="1" t="inlineStr">
+        <is>
+          <t>280-226133</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
         <is>
           <t>Completada desde bienes santa sofia (2).xlsx</t>
         </is>
       </c>
     </row>
-    <row r="237">
-      <c r="B237" t="inlineStr">
-        <is>
-          <t>Moto Privada (Etapa II)</t>
-        </is>
-      </c>
-      <c r="C237" t="inlineStr">
-        <is>
-          <t>Moto 74</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr">
-        <is>
-          <t>Patio de Motos (Segunda Etapa)</t>
-        </is>
-      </c>
-      <c r="E237" t="inlineStr">
-        <is>
-          <t>1.60</t>
-        </is>
-      </c>
-      <c r="F237" t="inlineStr">
-        <is>
-          <t>0.024%</t>
-        </is>
-      </c>
-      <c r="G237" t="inlineStr">
-        <is>
-          <t>0.013%</t>
-        </is>
-      </c>
-      <c r="H237" s="1" t="inlineStr">
-        <is>
-          <t>280-226131</t>
-        </is>
-      </c>
-      <c r="I237" t="inlineStr">
-        <is>
-          <t>Completada desde bienes santa sofia (2).xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="238">
-      <c r="B238" t="inlineStr">
-        <is>
-          <t>Moto Privada (Etapa II)</t>
-        </is>
-      </c>
-      <c r="C238" t="inlineStr">
-        <is>
-          <t>Moto 75</t>
-        </is>
-      </c>
-      <c r="D238" t="inlineStr">
-        <is>
-          <t>Patio de Motos (Segunda Etapa)</t>
-        </is>
-      </c>
-      <c r="E238" t="inlineStr">
-        <is>
-          <t>1.60</t>
-        </is>
-      </c>
-      <c r="F238" t="inlineStr">
-        <is>
-          <t>0.024%</t>
-        </is>
-      </c>
-      <c r="G238" t="inlineStr">
-        <is>
-          <t>0.013%</t>
-        </is>
-      </c>
-      <c r="H238" s="1" t="inlineStr">
-        <is>
-          <t>280-226132</t>
-        </is>
-      </c>
-      <c r="I238" t="inlineStr">
-        <is>
-          <t>Completada desde bienes santa sofia (2).xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="239">
-      <c r="B239" t="inlineStr">
-        <is>
-          <t>Moto Privada (Etapa II)</t>
-        </is>
-      </c>
-      <c r="C239" t="inlineStr">
-        <is>
-          <t>Moto 76</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr">
-        <is>
-          <t>Patio de Motos (Segunda Etapa)</t>
-        </is>
-      </c>
-      <c r="E239" t="inlineStr">
-        <is>
-          <t>1.60</t>
-        </is>
-      </c>
-      <c r="F239" t="inlineStr">
-        <is>
-          <t>0.024%</t>
-        </is>
-      </c>
-      <c r="G239" t="inlineStr">
-        <is>
-          <t>0.013%</t>
-        </is>
-      </c>
-      <c r="H239" s="1" t="inlineStr">
-        <is>
-          <t>280-226133</t>
-        </is>
-      </c>
-      <c r="I239" t="inlineStr">
-        <is>
-          <t>Completada desde bienes santa sofia (2).xlsx</t>
-        </is>
-      </c>
-    </row>
     <row r="240">
+      <c r="A240" t="inlineStr"/>
       <c r="B240" t="inlineStr">
         <is>
           <t>TOTAL PARQUEADEROS (234)</t>
         </is>
       </c>
+      <c r="C240" t="inlineStr"/>
+      <c r="D240" t="inlineStr"/>
       <c r="E240" t="inlineStr">
         <is>
           <t>1,287.40</t>
@@ -20037,6 +20505,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
+      <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
           <t>SANTA SOFÍA CLUB RESIDENCIAL</t>
@@ -20044,6 +20513,7 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
           <t>SISTEMA DE CONTROL Y REGISTRO DE MATRÍCULAS INMOBILIARIAS</t>
@@ -20051,6 +20521,7 @@
       </c>
     </row>
     <row r="4">
+      <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
           <t>Generated Sep 2026 | v1.0 | Base de datos master de la copropiedad</t>
@@ -20058,6 +20529,7 @@
       </c>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
           <t>RANGOS OFICIALES DE MATRÍCULAS INMOBILIARIAS (SEGÚN ESCRITURAS)</t>
@@ -20065,6 +20537,7 @@
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
           <t>Etapa</t>
@@ -20092,6 +20565,7 @@
       </c>
     </row>
     <row r="8">
+      <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
           <t>Etapa I (Fase 1)</t>
@@ -20119,6 +20593,7 @@
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
           <t>Etapa II (Fase 2)</t>
@@ -20146,6 +20621,7 @@
       </c>
     </row>
     <row r="12">
+      <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
           <t>CONVENCIÓN DE COLORES PARA LA ADMINISTRACIÓN</t>
@@ -20153,6 +20629,7 @@
       </c>
     </row>
     <row r="13">
+      <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
           <t>Celda de Entrada (Light Blue)</t>
@@ -20165,6 +20642,7 @@
       </c>
     </row>
     <row r="14">
+      <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
           <t>Celda Calculada (Light Green)</t>
@@ -20177,6 +20655,7 @@
       </c>
     </row>
     <row r="17">
+      <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
           <t>ESTADÍSTICAS GENERALES DE UNIDADES PRIVADAS</t>
@@ -20184,6 +20663,7 @@
       </c>
     </row>
     <row r="18">
+      <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
           <t>Tipo de Unidad</t>
@@ -20211,6 +20691,7 @@
       </c>
     </row>
     <row r="19">
+      <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
           <t>Apartamentos Torre 1 (Bloques 1, 2, 3 y 4)</t>
@@ -20238,6 +20719,7 @@
       </c>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
           <t>Parqueaderos de Carros Privados</t>
@@ -20265,6 +20747,7 @@
       </c>
     </row>
     <row r="21">
+      <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
           <t>Parqueaderos de Motos Privados</t>
@@ -20292,6 +20775,7 @@
       </c>
     </row>
     <row r="22">
+      <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
           <t>Gran Total Copropiedad</t>

--- a/data/matriculas_santa_sofia_OFICIAL.xlsx
+++ b/data/matriculas_santa_sofia_OFICIAL.xlsx
@@ -28,7 +28,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -38,6 +38,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4CCCC"/>
       </patternFill>
     </fill>
   </fills>
@@ -53,9 +58,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -6634,7 +6640,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I230"/>
+  <dimension ref="A1:I229"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13055,14 +13061,14 @@
       <c r="E207" t="inlineStr"/>
       <c r="F207" t="inlineStr"/>
       <c r="G207" t="inlineStr"/>
-      <c r="H207" s="1" t="inlineStr">
-        <is>
-          <t>280-226125</t>
+      <c r="H207" s="2" t="inlineStr">
+        <is>
+          <t>280-21XXXX</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>CONFIRMADO</t>
+          <t>AMBIGUA: revisar manualmente opciones 280-226117, 280-226125</t>
         </is>
       </c>
     </row>
@@ -13292,12 +13298,12 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Moto 60</t>
+          <t>Moto 59</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>PARQUEADERO MOTO # 60 SEGUNDA ETAPA</t>
+          <t>PARQUEADERO MOTO # 59 SEGUNDA ETAPA</t>
         </is>
       </c>
       <c r="E215" t="inlineStr"/>
@@ -13305,7 +13311,7 @@
       <c r="G215" t="inlineStr"/>
       <c r="H215" s="1" t="inlineStr">
         <is>
-          <t>280-226117</t>
+          <t>280-226116</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -13323,12 +13329,12 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Moto 59</t>
+          <t>Moto 58</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>PARQUEADERO MOTO # 59 SEGUNDA ETAPA</t>
+          <t>PARQUEADERO MOTO # 58 SEGUNDA ETAPA</t>
         </is>
       </c>
       <c r="E216" t="inlineStr"/>
@@ -13336,7 +13342,7 @@
       <c r="G216" t="inlineStr"/>
       <c r="H216" s="1" t="inlineStr">
         <is>
-          <t>280-226116</t>
+          <t>280-226115</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -13354,12 +13360,12 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Moto 58</t>
+          <t>Moto 57</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>PARQUEADERO MOTO # 58 SEGUNDA ETAPA</t>
+          <t>PARQUEADERO MOTO # 57 SEGUNDA ETAPA</t>
         </is>
       </c>
       <c r="E217" t="inlineStr"/>
@@ -13367,7 +13373,7 @@
       <c r="G217" t="inlineStr"/>
       <c r="H217" s="1" t="inlineStr">
         <is>
-          <t>280-226115</t>
+          <t>280-226114</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -13385,12 +13391,12 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Moto 57</t>
+          <t>Moto 56</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>PARQUEADERO MOTO # 57 SEGUNDA ETAPA</t>
+          <t>PARQUEADERO MOTO # 56 SEGUNDA ETAPA</t>
         </is>
       </c>
       <c r="E218" t="inlineStr"/>
@@ -13398,7 +13404,7 @@
       <c r="G218" t="inlineStr"/>
       <c r="H218" s="1" t="inlineStr">
         <is>
-          <t>280-226114</t>
+          <t>280-226113</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -13416,12 +13422,12 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Moto 56</t>
+          <t>Moto 55</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>PARQUEADERO MOTO # 56 SEGUNDA ETAPA</t>
+          <t>PARQUEADERO MOTO # 55 SEGUNDA ETAPA</t>
         </is>
       </c>
       <c r="E219" t="inlineStr"/>
@@ -13429,7 +13435,7 @@
       <c r="G219" t="inlineStr"/>
       <c r="H219" s="1" t="inlineStr">
         <is>
-          <t>280-226113</t>
+          <t>280-226112</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -13447,12 +13453,12 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Moto 55</t>
+          <t>Moto 43</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>PARQUEADERO MOTO # 55 SEGUNDA ETAPA</t>
+          <t>PARQUEADERO MOTO # 43 SEGUNDA ETAPA</t>
         </is>
       </c>
       <c r="E220" t="inlineStr"/>
@@ -13460,7 +13466,7 @@
       <c r="G220" t="inlineStr"/>
       <c r="H220" s="1" t="inlineStr">
         <is>
-          <t>280-226112</t>
+          <t>280-226111</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -13478,12 +13484,12 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Moto 43</t>
+          <t>Moto 42</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>PARQUEADERO MOTO # 43 SEGUNDA ETAPA</t>
+          <t>PARQUEADERO MOTO # 42 SEGUNDA ETAPA</t>
         </is>
       </c>
       <c r="E221" t="inlineStr"/>
@@ -13491,7 +13497,7 @@
       <c r="G221" t="inlineStr"/>
       <c r="H221" s="1" t="inlineStr">
         <is>
-          <t>280-226111</t>
+          <t>280-226110</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -13509,12 +13515,12 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Moto 42</t>
+          <t>Moto 41</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>PARQUEADERO MOTO # 42 SEGUNDA ETAPA</t>
+          <t>PARQUEADERO MOTO # 41 SEGUNDA ETAPA</t>
         </is>
       </c>
       <c r="E222" t="inlineStr"/>
@@ -13522,7 +13528,7 @@
       <c r="G222" t="inlineStr"/>
       <c r="H222" s="1" t="inlineStr">
         <is>
-          <t>280-226110</t>
+          <t>280-226109</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -13540,12 +13546,12 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Moto 41</t>
+          <t>Moto 40</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>PARQUEADERO MOTO # 41 SEGUNDA ETAPA</t>
+          <t>PARQUEADERO MOTO # 40 SEGUNDA ETAPA</t>
         </is>
       </c>
       <c r="E223" t="inlineStr"/>
@@ -13553,7 +13559,7 @@
       <c r="G223" t="inlineStr"/>
       <c r="H223" s="1" t="inlineStr">
         <is>
-          <t>280-226109</t>
+          <t>280-226108</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -13571,12 +13577,12 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Moto 40</t>
+          <t>Moto 39</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>PARQUEADERO MOTO # 40 SEGUNDA ETAPA</t>
+          <t>PARQUEADERO MOTO # 39 SEGUNDA ETAPA</t>
         </is>
       </c>
       <c r="E224" t="inlineStr"/>
@@ -13584,7 +13590,7 @@
       <c r="G224" t="inlineStr"/>
       <c r="H224" s="1" t="inlineStr">
         <is>
-          <t>280-226108</t>
+          <t>280-226107</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -13602,12 +13608,12 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Moto 39</t>
+          <t>Moto 38</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>PARQUEADERO MOTO # 39 SEGUNDA ETAPA</t>
+          <t>PARQUEADERO MOTO # 38 SEGUNDA ETAPA</t>
         </is>
       </c>
       <c r="E225" t="inlineStr"/>
@@ -13615,7 +13621,7 @@
       <c r="G225" t="inlineStr"/>
       <c r="H225" s="1" t="inlineStr">
         <is>
-          <t>280-226107</t>
+          <t>280-226106</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -13633,12 +13639,12 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Moto 38</t>
+          <t>Moto 37</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>PARQUEADERO MOTO # 38 SEGUNDA ETAPA</t>
+          <t>PARQUEADERO MOTO # 37 SEGUNDA ETAPA</t>
         </is>
       </c>
       <c r="E226" t="inlineStr"/>
@@ -13646,7 +13652,7 @@
       <c r="G226" t="inlineStr"/>
       <c r="H226" s="1" t="inlineStr">
         <is>
-          <t>280-226106</t>
+          <t>280-226105</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -13664,12 +13670,12 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Moto 37</t>
+          <t>Moto 36</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>PARQUEADERO MOTO # 37 SEGUNDA ETAPA</t>
+          <t>PARQUEADERO MOTO # 36 SEGUNDA ETAPA</t>
         </is>
       </c>
       <c r="E227" t="inlineStr"/>
@@ -13677,7 +13683,7 @@
       <c r="G227" t="inlineStr"/>
       <c r="H227" s="1" t="inlineStr">
         <is>
-          <t>280-226105</t>
+          <t>280-226104</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -13695,12 +13701,12 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Moto 36</t>
+          <t>Moto 35</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>PARQUEADERO MOTO # 36 SEGUNDA ETAPA</t>
+          <t>PARQUEADERO MOTO # 35 SEGUNDA ETAPA</t>
         </is>
       </c>
       <c r="E228" t="inlineStr"/>
@@ -13708,7 +13714,7 @@
       <c r="G228" t="inlineStr"/>
       <c r="H228" s="1" t="inlineStr">
         <is>
-          <t>280-226104</t>
+          <t>280-226103</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -13726,12 +13732,12 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Moto 35</t>
+          <t>Moto 34</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>PARQUEADERO MOTO # 35 SEGUNDA ETAPA</t>
+          <t>PARQUEADERO MOTO # 34 SEGUNDA ETAPA</t>
         </is>
       </c>
       <c r="E229" t="inlineStr"/>
@@ -13739,41 +13745,10 @@
       <c r="G229" t="inlineStr"/>
       <c r="H229" s="1" t="inlineStr">
         <is>
-          <t>280-226103</t>
+          <t>280-226102</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
-        <is>
-          <t>CONFIRMADO</t>
-        </is>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="inlineStr"/>
-      <c r="B230" t="inlineStr">
-        <is>
-          <t>Moto Privada (Etapa I)</t>
-        </is>
-      </c>
-      <c r="C230" t="inlineStr">
-        <is>
-          <t>Moto 34</t>
-        </is>
-      </c>
-      <c r="D230" t="inlineStr">
-        <is>
-          <t>PARQUEADERO MOTO # 34 SEGUNDA ETAPA</t>
-        </is>
-      </c>
-      <c r="E230" t="inlineStr"/>
-      <c r="F230" t="inlineStr"/>
-      <c r="G230" t="inlineStr"/>
-      <c r="H230" s="1" t="inlineStr">
-        <is>
-          <t>280-226102</t>
-        </is>
-      </c>
-      <c r="I230" t="inlineStr">
         <is>
           <t>CONFIRMADO</t>
         </is>
